--- a/기획안/혼합안_중국_우크라이나_일본.xlsx
+++ b/기획안/혼합안_중국_우크라이나_일본.xlsx
@@ -9742,7 +9742,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F177"/>
+  <dimension ref="A1:F180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9839,97 +9839,133 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="75" customHeight="1">
+    <row r="10" ht="18" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
+          <t>공동 주인공</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>쑤민 (苏敏)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>공동 주인공 경로</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>인권변호사(한서우이 사무소, 토지·이주 사건) → 법률원조센터 '명등' 공동대표 → 일제 연행·TV 자백 거부 → '국가정권 전복 선동'으로 징역 3년 → 출소·변호사 자격 박탈·출국 금지 → '공민 대리인'으로 탕쉐 변론, 지하 법률원조망 '잉훠' 조직 → 연금·강제 '여행' → '청원 행동' 명단에 올라 재구금(선즈위안 정부의 공문) → 석방 후 감시 속 '제자리 망명' 활동가, '사면 아닌 복권' 요구 → 새 지도부의 첫 결정으로 법적 복권·자격 회복 → 창촨시 법률원조센터 창구 변호사</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>공동 주인공 최종</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>창촨시 법률원조센터 창구 변호사(복권 후 변호사 자격 회복)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="75" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
           <t>마모</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>마모가 두 갈래로 나뉜다. 안의 마모 — 선즈위안은 석방 보증서, 탕쉐 이송을 막지 못한 늦은 전화, 쑤민을 다시 가둔 자기 이름의 공문, 마지막으로 연임 캠페인에 대한 침묵으로 조금씩 '그들의 말'로 말하게 된다. 밖의 마모 — 쑤민은 감옥, 자격 박탈, 가족이 치르는 대가, 동료들의 이탈, 끝없는 감시 속에서 고립과 날 선 원칙만 남는다. 부마다 한 사람씩 잃는다: 스승 한서우이(1부), 두 사람의 동행과 동료들의 자유(2부), 아버지 선궈칭·기자 예란(3부), 활동가 탕쉐(4부 옥중 사망), 친구 가오밍저(5부), 감사관 우슈전(6부), 쑤민의 자유를 빼앗은 자기 확신(7부), 정치밍(8부), 커팅웨(9부), 간화이구와 '스스로 떠나는 사람'이라는 자기 서사(10부).</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="45" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
+    <row r="14" ht="45" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>권력의 유혹</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>두 번 온다. 7부 총서기 첫해의 복합위기 속에서 사오톄쥔이 '청원 행동' 영도소조의 초법적 권한과 임기 제한 폐지를 내밀고 — 그는 자기 이름의 공문으로 쑤민이 다시 끌려간 것을 보고 나서야 거절한다. 10부 2기 마지막 해, 대홍수와 지방은행 예금 동결 사태가 겹친 진짜 위기 앞에서 유혹은 '일을 끝내려면 한 임기만 더'라는 가장 그럴듯한 얼굴로 돌아온다. 이번에는 거절하지 않는다 — 측근들이 연임 요청 결의와 '영수' 호칭을 시작하도록 침묵으로 내버려 둔다.</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="60" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
+    <row r="15" ht="60" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>자기 제한</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>8부 '권력의 경계' 패키지: 총서기·국가주석 연속 2기 제한, 위기 결정의 상무위원회 다수결, 지정거소감시거주의 기간·장소 제한(쑤민의 익명 수정 의견 반영), 그리고 그가 직접 써 넣은 '총서기 해임 절차'(정치국원 3분의 1 발의 → 정치국 확대회의 → 중앙위원회 전체회의 과반 표결). 10부에서 개인의 자기 제한은 실패하지만 제도화된 자기 제한이 그를 멈춘다. 그의 마지막 자기 제한은 단 하나 — 사오톄쥔의 경호부대 동원 제안과 전체회의 연기 제안을 거절하고, 변론 없이 표결을 받아들이는 것.</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>결말 유형</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>자기가 만든 규칙에 의한 해임·승복</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="90" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
+    <row r="17" ht="90" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>결말</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>2기 마지막 해의 위기 속에 연임 캠페인이 번지자, 청시와 웨이창펑을 비롯한 정치국원 3분의 1 이상이 그가 8부에 써 넣은 해임 조항으로 동의안을 발의한다. 남방 요양지 란산에 머물던 그는 '홍수 보고'를 명목으로 베이징 확대회의에 불려 오고(1964년 10월의 메아리 — 모티프로만), 웨이창펑이 조항을 읽고 청시가 사유를 읽는다. 그는 변론하지 않고, 이튿날 중앙위원회 전체회의 과반 표결로 해임된다. '건강상 이유'로 발표하자는 배려를 거절하고 '규정에 따른 해임'이라고 쓰게 한 것이 그의 마지막 결정이다. 무력도 유혈도 없는 이양 — 규칙이 그 규칙을 쓴 사람보다 강하다는 증명. 청시 지도부의 첫 결정은 쑤민과 잉훠 동료들의 법적 복권이다. 에필로그(5년 뒤): 평당원 선즈위안이 번호표를 들고 창촨 법률원조 창구 앞에 줄을 서고, 창구의 쑤민이 그에게 먼저 차를 따른다. 같은 해 청시는 한 번의 임기 뒤 녜추에게 정해진 날 권력을 넘긴다.</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="150" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
+    <row r="18" ht="150" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>구성·무게중심</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>10부 × 12화 + 에필로그. 원작 9부를 10부로 늘린 CN안(당내 사다리)을 바탕으로, 원작의 '변절자' 선택을 한 사무소의 두 제자에게 쪼갠 이중 주인공 판이다. 선즈위안은 안의 사다리(현→시→성→중앙→총서기)를, 쑤민은 밖의 사다리(변호사→구금→출소→지하 법률원조→제자리 망명 활동가)를 오르며, 부마다 무게가 번갈아 놓인다: 1·2부 공동, 3·6·8부는 홀수 화가 쑤민 시점([쑤민] 표시), 4부는 쑤민 중심(탕쉐의 옥중 사망), 5·7·9부는 선즈위안 중심(쑤민은 1~2화), 10부는 다시 교차. 두 사람은 네 번만 만나고 매번이 전환점이다 — 2부 12화 접견실 유리 너머(갈라섬), 4부 7화 탕쉐의 장례(안에서 무엇을 막았나), 7부 10화 지정거소 시설(그가 전권을 내려놓는 계기), 에필로그의 창구. 그 사이는 서랍 속 부치지 못한 편지와 메이뤄란이 전하는 구두 전언뿐이다. 원작 4부의 옥중 사망은 쑤민 대신 신규 인물 탕쉐(산골 교사·토지권 활동가)가 넘겨받고, 쑤민은 끝까지 살아 '바깥의 양심'이 된다. 확장: 쑤민의 감옥·출소·잉훠·재구금 서사(신규 약 20화), 8부의 해임 조항 입안(8부 4화), 10부 전체(위기→연임 묵인→확대회의→표결→복권). 축소·삭제: 가오밍저 배신 발각과 커팅웨 담판(3부), 브레이크 사고(4부), 원로들의 여름·청시의 첫 발언(6부 압축), 정치적 대가(7부 11화, 12화에 흡수), 대회 연기·회의장 봉쇄와 귀향 열차(원 CN안 10부). 결말은 '자진 퇴장'에서 '자기가 만든 규칙에 의한 해임·승복'으로 뒤집혔다 — 그는 스스로 떠나는 데 실패하지만, 그가 써 둔 규칙이 그를 대신해 떠나게 한다.</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="75" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
+    <row r="19" ht="75" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>작은 모티프</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>'先喝杯茶，再说事'(먼저 차부터, 일은 그다음). 한서우이는 의뢰인에게 늘 먼저 차를 따르고, 중국어의 '喝茶(차 마시기)'는 공안·국가안전의 소환을 뜻하는 완곡어('被喝茶')이기도 하다. 1부 장례식에서 두 제자는 스승의 찻잔 두 개를 하나씩 나눠 갖는다 — 선즈위안의 잔은 집무실 서랍 속 부치지 못한 편지 위에, 쑤민의 잔은 감옥·연금 아파트·이동 창구를 따라다닌다. 7부 지정거소 시설에서 쑤민은 그에게 '차 마실래? 여긴 너희가 차 마시자고 부르는 곳이잖아'라고 묻는다. 우슈전의 메모 '别忘了茶(차를 잊지 마)'가 8부에 해독되고, 에필로그에서 소환의 '차'는 진짜 차로 뒤집힌다 — 권력을 잃고 줄을 선 사람에게, 그가 가두었던 사람이 먼저 차를 낸다.</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="225" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
+    <row r="20" ht="225" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>실제 현안</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>· 인권변호사 일제 연행 10년 뒤에도 이어지는 변호사 자격 박탈·출국 금지·가족 괴롭힘, 책임자 불처벌
 · 지정거소감시거주·TV 자백 강요와 가족에 대한 압박(연금·공직·학업 불이익)
@@ -9944,13 +9980,13 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="525" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
+    <row r="21" ht="525" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>현안 출처(웹 확인)</t>
         </is>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>· 709 사건 10년: 약 50명 인권변호사 자격 박탈, 연행·괴롭힘 지속 — Human Rights Watch, 2025-07-06, https://www.hrw.org/news/2025/07/06/china-10-years-since-709-crackdown-lawyers-still-under-fire
 · 지방정부 숨은 부채를 중앙 재정으로 '정리'하는 방식의 한계 — Carnegie Endowment, 2025-08, https://carnegieendowment.org/posts/2025/08/using-chinas-central-government-balance-sheet-to-clean-up-local-government-debt-is-a-bad-idea?lang=en
@@ -9967,13 +10003,13 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="180" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
+    <row r="22" ht="180" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>인용 자원</t>
         </is>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>· 루쉰 『외침(呐喊)』 자서 — '쇠로 된 방(铁屋子)' 비유: 깨어난 몇 사람이 창문 없는 방을 부술 희망
 · 루쉰 「고향(故乡)」 — '其实地上本没有路，走的人多了，也便成了路'
@@ -9986,161 +10022,77 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="210" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
+    <row r="23" ht="210" customHeight="1">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>민감도·주의</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B23" s="8" t="inlineStr">
         <is>
           <t>최고 수준. 중국 본토에서 제작·방영이 불가능한 대체역사물로, 해외·홍콩·대만 제작이나 국제 스트리밍을 전제로 한다. 실존 지도자·실존 인권변호사·실제 사건명(특정 연도의 일제 연행 사건명, 실제 반부패 캠페인명, 실존 낙마 인물)을 쓰지 않고 연상되는 세부(고유 날짜·지명·어록)도 피한다. 특히 '임기 제한 복원과 해임 조항에 의한 퇴진' 결말이 현실 지도자에 대한 직접 풍자로 읽히지 않도록 연도·호칭·개헌 절차를 가상화하고, 주인공을 이상화된 구원자가 아니라 월권과 타협의 대가를 치르는 인물로 그린다. 10부의 해임은 무력·봉쇄 없는 당내 절차(발의·확대회의·전체회의 표결)로만 그려 쿠데타 스릴러로 소비되지 않게 하고, 1964년 10월의 메아리(휴가지 소환, 확대회의, 전체회의)는 구조적 모티프로만 쓰며 실존 인물·날짜·발언을 가져오지 않는다. 현실 지도부를 향한 '해임 처방'으로 읽히지 않도록 해임 조항 자체를 가상의 당내 규정으로 설정한다. 인권변호사가 입당해 최고위에 오르는 설정의 비현실성은 '입당 소개인' 간화이구의 비호와 성 차원의 전문인력 파견 실험으로 설명하고, 옛 동료들의 '변절자' 비판을 정면으로 다뤄 체제 미화로 읽히지 않게 한다. 민족 문제는 특정 민족을 겨냥하지 않도록 이주 문제를 가상 산골 마을로 처리. 고문·TV 자백 장면은 피해자 존엄을 해치지 않게 절제. 배우·스태프와 가족의 안전을 고려해 크레디트 정책을 사전에 정한다. [이중 주인공 주의점] 어느 길도 미화하지 않는다. 안의 길: 선즈위안의 석방 보증서, 탕쉐 이송을 막지 못한 늦은 전화, 쑤민을 다시 가둔 자기 이름의 공문, 연임 캠페인에 대한 침묵을 정면으로 보여 주고, 그의 개혁 성과가 그 대가를 상쇄하는 것처럼 편집하지 않는다. 밖의 길: 쑤민을 무결한 순교자로 만들지 않는다 — 가족(어머니·조카)이 치르는 대가, 그녀의 원칙 때문에 사면을 받지 못한 동료들의 원망, 고립이 만든 날 선 판단과 오판도 그린다. 그녀가 살아남는 것을 '체제가 결국 관대했다'는 메시지로 읽히게 하지 말고, 복권은 그녀가 아니라 규칙의 결과로 위치시킨다. 두 사람의 관계는 로맨스로 소비하지 않는다(편지와 전언은 논쟁과 증언의 형식). 쑤민은 실존 여성 인권변호사·활동가의 경력·사건·가족사를 조합하지 않도록 이력을 가상화하고, 옥중 사망(탕쉐)·지정거소 장면은 피해자 존엄을 해치지 않게 절제한다. 새 지도부의 첫 결정(복권)이 '선한 후계자' 판타지로 끝나지 않도록, 에필로그에 청시 역시 한 번의 임기로 떠나는 규칙의 반복을 함께 둔다.</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>2. 인물 대응표</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>원작 인물</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>현지 이름</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>한국어 표기</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
+      <c r="D26" s="3" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E23" s="3" t="inlineStr">
+      <c r="E26" s="3" t="inlineStr">
         <is>
           <t>운명</t>
         </is>
       </c>
-      <c r="F23" s="3" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>비코프(스승)</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>韩守义</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>한서우이</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>창촨시의 노변호사, 선즈위안과 쑤민의 스승. 1980년대 제방 부실을 고발한 기술자를 변호했다가 변호사 자격을 정지당한 과거(배경사). 의뢰인에게 늘 먼저 차를 따른다</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>1부 9화 '심흔자사' 혐의로 연행, 지정거소감시거주 중 심장약 중단, 11화 석방 직후 사망. 남긴 찻잔 두 개를 두 제자가 나눠 갖는다</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>올가(활동가) 확장 — 공동 주인공</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>苏敏</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>쑤민</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>한서우이 사무소의 변호사(토지·이주 사건) → 바깥의 양심. 선즈위안과 같은 스승 아래서 자란 동료이자 평생의 논쟁 상대</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>2부 9화 일제 연행, 11화 TV 자백 거부로 징역 3년, 3부 7화 출소·자격 박탈, 9화 지하 법률원조망 '잉훠' 조직, 4부 탕쉐의 공민 대리인, 7부 8화 '청원 행동' 명단으로 재구금, 8부 1화 석방 후 '제자리 망명', 10부 5화 공개 서한 뒤 연금, 11화 새 지도부의 첫 결정으로 복권, 에필로그 창구 변호사로 생존</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>올가(활동가) — 옥중 사망 역할 승계(신규 인물)</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>唐雪</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>탕쉐</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>희토류 광산 '생태이민'에 맞선 산골 마을 교사·토지권 활동가. 쑤민의 첫 의뢰인이자 끝내 지키지 못한 사람</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>1부 7화 등장, 2부 6화 구속, 3부 5화 옥중 편지, 4부 1화 재구속, 3화 옥중 단식, 5화 병원 이송 지연, 6화 단식 14일째 옥중 사망. 10부 11화 쑤민이 복권 통지서를 들고 그녀의 무덤을 찾는다</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr"/>
+      <c r="F26" s="3" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>파벨(친구)</t>
+          <t>비코프(스승)</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>高明哲</t>
+          <t>韩守义</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>가오밍저</t>
+          <t>한서우이</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>선즈위안의 소꿉친구, 국유기업 전문 로펌 변호사</t>
+          <t>창촨시의 노변호사, 선즈위안과 쑤민의 스승. 1980년대 제방 부실을 고발한 기술자를 변호했다가 변호사 자격을 정지당한 과거(배경사). 의뢰인에게 늘 먼저 차를 따른다</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>2부 5화 균열, 3부 2화 유출 고백, 10화 장부 사본을 지키고 대신 유치 조사, 5부 5화 사법 부패망 조사 중 구치소에서 '자살' 처리된 채 사망. 6화 그의 어머니가 쑤민에게 부검 요구 사건을 맡긴다</t>
+          <t>1부 9화 '심흔자사' 혐의로 연행, 지정거소감시거주 중 심장약 중단, 11화 석방 직후 사망. 남긴 찻잔 두 개를 두 제자가 나눠 갖는다</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr"/>
@@ -10148,27 +10100,27 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>다리야(기자)</t>
+          <t>올가(활동가) 확장 — 공동 주인공</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>叶澜</t>
+          <t>苏敏</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>예란</t>
+          <t>쑤민</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>『북원주간』 탐사기자, 두 주인공의 첫 사건부터 함께한 기록자</t>
+          <t>한서우이 사무소의 변호사(토지·이주 사건) → 바깥의 양심. 선즈위안과 같은 스승 아래서 자란 동료이자 평생의 논쟁 상대</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>3부 8화 칭허현 토지·채무 폭로 기사 공개 당일 실종, 5부 9화 실종 당일의 송금 사슬이 드러나며 살해 확정</t>
+          <t>2부 9화 일제 연행, 11화 TV 자백 거부로 징역 3년, 3부 7화 출소·자격 박탈, 9화 지하 법률원조망 '잉훠' 조직, 4부 탕쉐의 공민 대리인, 7부 8화 '청원 행동' 명단으로 재구금, 8부 1화 석방 후 '제자리 망명', 10부 5화 공개 서한 뒤 연금, 11화 새 지도부의 첫 결정으로 복권, 에필로그 창구 변호사로 생존</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr"/>
@@ -10176,27 +10128,27 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>니콜라이·안나(부모)</t>
+          <t>올가(활동가) — 옥중 사망 역할 승계(신규 인물)</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>沈国庆 / 周秀兰</t>
+          <t>唐雪</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>선궈칭 / 저우슈란</t>
+          <t>탕쉐</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>선궈칭: 화학공장 정비공 출신 퇴직 노동자, 오랜 당원 / 저우슈란: 어머니, 가족의 중재자</t>
+          <t>희토류 광산 '생태이민'에 맞선 산골 마을 교사·토지권 활동가. 쑤민의 첫 의뢰인이자 끝내 지키지 못한 사람</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>선궈칭: 2부 8화 연금·당적 조사 압박, 10화 아들의 석방을 탄원하는 편지(아들이 보증서에 서명하게 된 배경), 3부 6화 뇌졸중으로 사망 / 저우슈란: 10부 12화 해임된 아들을 창촨 아파트에서 맞고, 에필로그 전 화면 밖에서 조용히 세상을 떠남</t>
+          <t>1부 7화 등장, 2부 6화 구속, 3부 5화 옥중 편지, 4부 1화 재구속, 3화 옥중 단식, 5화 병원 이송 지연, 6화 단식 14일째 옥중 사망. 10부 11화 쑤민이 복권 통지서를 들고 그녀의 무덤을 찾는다</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr"/>
@@ -10204,27 +10156,27 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>리트비노프(재벌)</t>
+          <t>파벨(친구)</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>骆振邦</t>
+          <t>高明哲</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>뤄전방</t>
+          <t>가오밍저</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>혁명원로의 아들, 국유 북원광업그룹 회장('태자당' 재벌). 탕쉐 마을 광산의 실소유자</t>
+          <t>선즈위안의 소꿉친구, 국유기업 전문 로펌 변호사</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>4부 10화 선즈위안에게 광산을 대가로 접근, 5부 8화 출국 직전 연행, 8부 11화 공개재판 판결과 해외 은닉자산 환수</t>
+          <t>2부 5화 균열, 3부 2화 유출 고백, 10화 장부 사본을 지키고 대신 유치 조사, 5부 5화 사법 부패망 조사 중 구치소에서 '자살' 처리된 채 사망. 6화 그의 어머니가 쑤민에게 부검 요구 사건을 맡긴다</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr"/>
@@ -10232,27 +10184,27 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>크릴로프(보안기관)</t>
+          <t>다리야(기자)</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>柯庭岳</t>
+          <t>叶澜</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>커팅웨</t>
+          <t>예란</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>창촨시·북원성 정법위 서기 → 중앙 정법 계통 고위직. '차 마시자'고 부르는 사람, 두 제자 모두를 불렀던 사람</t>
+          <t>『북원주간』 탐사기자, 두 주인공의 첫 사건부터 함께한 기록자</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>1부 8화 한서우이 소환, 2부 7화 거래 제안, 4부 8화 무장경찰 투입 거부, 5부 9화 자진 사임, 8부 6화 마지막 대화, 9부 6화 병사 — 홀로 조문한 선즈위안에게 '규칙은 사람을 가리지 않는다, 당신도'라는 봉투를 남김</t>
+          <t>3부 8화 칭허현 토지·채무 폭로 기사 공개 당일 실종, 5부 9화 실종 당일의 송금 사슬이 드러나며 살해 확정</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr"/>
@@ -10260,27 +10212,27 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>이리나(후계자)</t>
+          <t>니콜라이·안나(부모)</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>程曦</t>
+          <t>沈国庆 / 周秀兰</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>청시</t>
+          <t>선궈칭 / 저우슈란</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>법대생 선조생 → 성장 비서 → 총서기 판공청 주임 → 후계자. 선즈위안이 만든 규칙을 그에게 적용하는 사람</t>
+          <t>선궈칭: 화학공장 정비공 출신 퇴직 노동자, 오랜 당원 / 저우슈란: 어머니, 가족의 중재자</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>4부 4화 등장, 6부 6화 폭발로 부상, 7부 9화 정면 대결, 8부 4화 해임 조항을 '당신 자신에게 겨눈 총'이라 부름, 9부 8화 공개 경쟁 추천으로 후계 후보, 10부 7화 쑤민을 사적으로 방문, 9화 확대회의에서 해임 사유 낭독, 10화 총서기 선출, 11화 첫 결정으로 쑤민 복권, 에필로그 한 번의 임기 뒤 녜추에게 규칙대로 이양</t>
+          <t>선궈칭: 2부 8화 연금·당적 조사 압박, 10화 아들의 석방을 탄원하는 편지(아들이 보증서에 서명하게 된 배경), 3부 6화 뇌졸중으로 사망 / 저우슈란: 10부 12화 해임된 아들을 창촨 아파트에서 맞고, 에필로그 전 화면 밖에서 조용히 세상을 떠남</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr"/>
@@ -10288,27 +10240,27 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>카탸(최측근 실무자)</t>
+          <t>리트비노프(재벌)</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>李雨桐</t>
+          <t>骆振邦</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>리위퉁</t>
+          <t>뤄전방</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>명등 법률원조센터 자원활동가 출신, 선즈위안의 실무 참모. 안과 밖 양쪽의 사정을 다 아는 사람</t>
+          <t>혁명원로의 아들, 국유 북원광업그룹 회장('태자당' 재벌). 탕쉐 마을 광산의 실소유자</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>2부 1화 명등 합류, 3부 2화 '변절자' 선즈위안 곁에 남음, 9부 3화 낙인 조례 폐지로 명예 회복, 10부 12화 해임 뒤 사직, 에필로그 창촨 창구에서 쑤민의 옆자리</t>
+          <t>4부 10화 선즈위안에게 광산을 대가로 접근, 5부 8화 출국 직전 연행, 8부 11화 공개재판 판결과 해외 은닉자산 환수</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr"/>
@@ -10316,27 +10268,27 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>그레벤시코프(정치 원로)</t>
+          <t>크릴로프(보안기관)</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>甘怀谷</t>
+          <t>柯庭岳</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>간화이구</t>
+          <t>커팅웨</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>은퇴한 개혁파 원로 간부, 선즈위안의 입당 소개인</t>
+          <t>창촨시·북원성 정법위 서기 → 중앙 정법 계통 고위직. '차 마시자'고 부르는 사람, 두 제자 모두를 불렀던 사람</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>2부 10화 석방 탄원, 12화 접견 주선·입당 소개인, 7부 12화 '이제야 네가 돌아왔다', 10부 3화 병사 — '들어오는 법은 내가 가르쳤다, 나가는 법은 네가 보여 달라'는 마지막 당부를 선즈위안은 지키지 못한다</t>
+          <t>1부 8화 한서우이 소환, 2부 7화 거래 제안, 4부 8화 무장경찰 투입 거부, 5부 9화 자진 사임, 8부 6화 마지막 대화, 9부 6화 병사 — 홀로 조문한 선즈위안에게 '규칙은 사람을 가리지 않는다, 당신도'라는 봉투를 남김</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr"/>
@@ -10344,27 +10296,27 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>이졸다·키릴(감사팀)</t>
+          <t>이리나(후계자)</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>邬秀珍 / 郑启明</t>
+          <t>程曦</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>우슈전 / 정치밍</t>
+          <t>청시</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>우슈전: 성 감사청 출신 베테랑 감사관, 손님에게 먼저 차를 내는 사람 / 정치밍: 감사팀장 → 국가재정투명국 국장</t>
+          <t>법대생 선조생 → 성장 비서 → 총서기 판공청 주임 → 후계자. 선즈위안이 만든 규칙을 그에게 적용하는 사람</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>우슈전: 6부 6화 시찰장 폭발로 사망, 8부 12화 '别忘了茶' 메모 해독 / 정치밍: 8부 8화 총공세 속 과로로 사망</t>
+          <t>4부 4화 등장, 6부 6화 폭발로 부상, 7부 9화 정면 대결, 8부 4화 해임 조항을 '당신 자신에게 겨눈 총'이라 부름, 9부 8화 공개 경쟁 추천으로 후계 후보, 10부 7화 쑤민을 사적으로 방문, 9화 확대회의에서 해임 사유 낭독, 10화 총서기 선출, 11화 첫 결정으로 쑤민 복권, 에필로그 한 번의 임기 뒤 녜추에게 규칙대로 이양</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr"/>
@@ -10372,27 +10324,27 @@
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>조야(기록 보관자)</t>
+          <t>카탸(최측근 실무자)</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>梅若兰</t>
+          <t>李雨桐</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>메이뤄란</t>
+          <t>리위퉁</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>한서우이의 35년 지기, 은퇴한 변호사협회 서기. 1980년대 사건 기록 보관자이자 두 주인공 사이의 유일한 전령(구두 전언만 전한다)</t>
+          <t>명등 법률원조센터 자원활동가 출신, 선즈위안의 실무 참모. 안과 밖 양쪽의 사정을 다 아는 사람</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>3부 3화 첫 면회부터 전령, 4부 3화 쑤민의 한 줄 '이송을 막지 마'를 전함, 7부 10화 한서우이 기록과 쑤민의 행방을 함께 건넴, 10부 5화 쑤민의 공개 서한 전달, 12화 부치지 못한 편지 묶음을 맡아 보관, 에필로그까지 생존</t>
+          <t>2부 1화 명등 합류, 3부 2화 '변절자' 선즈위안 곁에 남음, 9부 3화 낙인 조례 폐지로 명예 회복, 10부 12화 해임 뒤 사직, 에필로그 창촨 창구에서 쑤민의 옆자리</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr"/>
@@ -10400,27 +10352,27 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>마리나 젤레즈냐크(차기 지도자)</t>
+          <t>그레벤시코프(정치 원로)</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>聂秋</t>
+          <t>甘怀谷</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>녜추</t>
+          <t>간화이구</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>희토류 산지 서수이성 부성장, 성 채무 내부고발자 → 서수이성 서기 → 판공청 주임</t>
+          <t>은퇴한 개혁파 원로 간부, 선즈위안의 입당 소개인</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>5부 4화 내부고발, 8부 9화 서수이성 부채 공개(교사 임금 소송의 쑤민과 처음 만남), 9부 9화 판공청 주임 후보, 에필로그 공개 경쟁 추천을 거쳐 총서기 취임</t>
+          <t>2부 10화 석방 탄원, 12화 접견 주선·입당 소개인, 7부 12화 '이제야 네가 돌아왔다', 10부 3화 병사 — '들어오는 법은 내가 가르쳤다, 나가는 법은 네가 보여 달라'는 마지막 당부를 선즈위안은 지키지 못한다</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr"/>
@@ -10428,27 +10380,27 @@
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>보구슬랍스키(자금원)</t>
+          <t>이졸다·키릴(감사팀)</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>顾延昭</t>
+          <t>邬秀珍 / 郑启明</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>구옌자오</t>
+          <t>우슈전 / 정치밍</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>재정부 부부장, 비밀 경비의 '지갑'</t>
+          <t>우슈전: 성 감사청 출신 베테랑 감사관, 손님에게 먼저 차를 내는 사람 / 정치밍: 감사팀장 → 국가재정투명국 국장</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>5부 1화 '1년 안에 당신은 여기 없을 것' 경고, 8부 12화 해외 도주, 9부 7화 송환되어 우슈전 폭발 자금원으로 기소</t>
+          <t>우슈전: 6부 6화 시찰장 폭발로 사망, 8부 12화 '别忘了茶' 메모 해독 / 정치밍: 8부 8화 총공세 속 과로로 사망</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr"/>
@@ -10456,27 +10408,27 @@
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>코발추크(경쟁자)</t>
+          <t>조야(기록 보관자)</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>魏长风</t>
+          <t>梅若兰</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>웨이창펑</t>
+          <t>메이뤄란</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>민족주의·포퓰리즘 성향의 정치국원, 총서기 자리의 경쟁자</t>
+          <t>한서우이의 35년 지기, 은퇴한 변호사협회 서기. 1980년대 사건 기록 보관자이자 두 주인공 사이의 유일한 전령(구두 전언만 전한다)</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>6부 12화 중앙위원회 표결에 승복, 9부 11화 사오톄쥔이 그를 버리고 선즈위안 쪽으로 가는 것을 지켜봄, 10부 9화 해임 동의안 공동 발의자로 확대회의에서 선즈위안이 쓴 조항을 읽음 — '당신이 쓴 규칙이다, 나도 졌을 때 따랐다'</t>
+          <t>3부 3화 첫 면회부터 전령, 4부 3화 쑤민의 한 줄 '이송을 막지 마'를 전함, 7부 10화 한서우이 기록과 쑤민의 행방을 함께 건넴, 10부 5화 쑤민의 공개 서한 전달, 12화 부치지 못한 편지 묶음을 맡아 보관, 에필로그까지 생존</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr"/>
@@ -10484,533 +10436,533 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
+          <t>마리나 젤레즈냐크(차기 지도자)</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>聂秋</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>녜추</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>희토류 산지 서수이성 부성장, 성 채무 내부고발자 → 서수이성 서기 → 판공청 주임</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>5부 4화 내부고발, 8부 9화 서수이성 부채 공개(교사 임금 소송의 쑤민과 처음 만남), 9부 9화 판공청 주임 후보, 에필로그 공개 경쟁 추천을 거쳐 총서기 취임</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>보구슬랍스키(자금원)</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>顾延昭</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>구옌자오</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>재정부 부부장, 비밀 경비의 '지갑'</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>5부 1화 '1년 안에 당신은 여기 없을 것' 경고, 8부 12화 해외 도주, 9부 7화 송환되어 우슈전 폭발 자금원으로 기소</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>코발추크(경쟁자)</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>魏长风</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>웨이창펑</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>민족주의·포퓰리즘 성향의 정치국원, 총서기 자리의 경쟁자</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>6부 12화 중앙위원회 표결에 승복, 9부 11화 사오톄쥔이 그를 버리고 선즈위안 쪽으로 가는 것을 지켜봄, 10부 9화 해임 동의안 공동 발의자로 확대회의에서 선즈위안이 쓴 조항을 읽음 — '당신이 쓴 규칙이다, 나도 졌을 때 따랐다'</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
           <t>라디셰프(유혹의 목소리)</t>
         </is>
       </c>
-      <c r="B40" s="4" t="inlineStr">
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>邵铁军</t>
         </is>
       </c>
-      <c r="C40" s="4" t="inlineStr">
+      <c r="C43" s="4" t="inlineStr">
         <is>
           <t>사오톄쥔</t>
         </is>
       </c>
-      <c r="D40" s="4" t="inlineStr">
+      <c r="D43" s="4" t="inlineStr">
         <is>
           <t>중앙국가안전위원회 판공실 주임, 강경파 측근. 7부 전권·임기 제한 폐지, 10부 3기 연임의 제안자</t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr">
+      <c r="E43" s="4" t="inlineStr">
         <is>
           <t>7부 12화 권한 축소를 받아들인 척, 9부 11화 '3기를 준비하자', 10부 4화 연임 요청 결의 주도, 8화 경호부대 동원을 제안했다가 거절당함, 12화 규정대로 기율 조사</t>
         </is>
       </c>
-      <c r="F40" s="4" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="6" t="inlineStr">
+      <c r="F43" s="4" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
         <is>
           <t>3. 부 구성</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="3" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
         <is>
           <t>부</t>
         </is>
       </c>
-      <c r="B43" s="3" t="inlineStr">
+      <c r="B46" s="3" t="inlineStr">
         <is>
           <t>제목(한국어)</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr">
+      <c r="C46" s="3" t="inlineStr">
         <is>
           <t>제목(현지어)</t>
         </is>
       </c>
-      <c r="D43" s="3" t="inlineStr">
+      <c r="D46" s="3" t="inlineStr">
         <is>
           <t>시기·주인공 신분</t>
         </is>
       </c>
-      <c r="E43" s="3" t="inlineStr">
+      <c r="E46" s="3" t="inlineStr">
         <is>
           <t>줄거리</t>
         </is>
       </c>
-      <c r="F43" s="3" t="inlineStr">
+      <c r="F46" s="3" t="inlineStr">
         <is>
           <t>핵심 상실</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t>1부</t>
-        </is>
-      </c>
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t>법정의 각성</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="inlineStr">
-        <is>
-          <t>法庭的觉醒</t>
-        </is>
-      </c>
-      <c r="D44" s="4" t="inlineStr">
-        <is>
-          <t>0년(2014년) / 선즈위안·쑤민: 창촨시 한서우이 법률사무소의 젊은 변호사</t>
-        </is>
-      </c>
-      <c r="E44" s="4" t="inlineStr">
-        <is>
-          <t>화학공장 폭발, 임금 체불, 폐수 오염, 산골 마을 강제 이주 사건을 스승 한서우이 아래서 나눠 맡으며 두 제자는 서로 다른 방식 — 조용한 증거 수집과 공개 탄원 — 을 익힌다. 커팅웨의 '차 마시자'는 호출 뒤 스승이 연행되어 숨지고, 두 사람은 스승의 찻잔 두 개를 하나씩 나눠 갖는다.</t>
-        </is>
-      </c>
-      <c r="F44" s="4" t="inlineStr">
-        <is>
-          <t>스승 한서우이</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="4" t="inlineStr">
-        <is>
-          <t>2부</t>
-        </is>
-      </c>
-      <c r="B45" s="4" t="inlineStr">
-        <is>
-          <t>유리 너머</t>
-        </is>
-      </c>
-      <c r="C45" s="4" t="inlineStr">
-        <is>
-          <t>隔着玻璃</t>
-        </is>
-      </c>
-      <c r="D45" s="4" t="inlineStr">
-        <is>
-          <t>0.5~1.5년(2015년) / 선즈위안·쑤민: 법률원조센터 '명등' 공동대표 → 선즈위안: 석방·입당 신청 / 쑤민: 구속·징역 3년</t>
-        </is>
-      </c>
-      <c r="E45" s="4" t="inlineStr">
-        <is>
-          <t>성도에서 '명등'을 연 두 사람은 돈의 유혹과 가족 압박, 탕쉐 사건을 함께 견디지만 어느 여름밤 함께 연행된다. 선즈위안은 아버지와 원로 간화이구의 탄원 끝에 '민감 사건 불수임' 보증서에 서명하고 나오고, 쑤민은 TV 자백을 거부하고 실형을 받는다. 입당 신청서를 품은 그가 접견실 유리 너머의 그녀를 만난다 — 첫 번째 만남, 갈라섬.</t>
-        </is>
-      </c>
-      <c r="F45" s="4" t="inlineStr">
-        <is>
-          <t>동료 변호사들의 자유, 두 사람의 동행</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="4" t="inlineStr">
-        <is>
-          <t>3부</t>
-        </is>
-      </c>
-      <c r="B46" s="4" t="inlineStr">
-        <is>
-          <t>안과 밖</t>
-        </is>
-      </c>
-      <c r="C46" s="4" t="inlineStr">
-        <is>
-          <t>里与外</t>
-        </is>
-      </c>
-      <c r="D46" s="4" t="inlineStr">
-        <is>
-          <t>1.5~6년(2015~2020년) / 선즈위안: 예비당원 → 칭허현 부현장(파견) → 현위서기 / 쑤민: 수감 → 출소(2018)·자격 박탈 → 지하 법률원조망 '잉훠' 조직</t>
-        </is>
-      </c>
-      <c r="E46" s="4" t="inlineStr">
-        <is>
-          <t>홀수 화는 감옥과 출소 뒤의 쑤민, 짝수 화는 '변절자' 선즈위안의 칭허현. 그가 융자플랫폼 부채와 토지 거래를 파헤치는 동안 아버지가 세상을 떠나고 예란이 사라지며, 그녀는 감방에서 상소장을 대신 쓰고 출소 뒤 자격 없이 지하 법률원조망 '잉훠'를 만든다. 메이뤄란이 두 사람 사이의 유일한 전령이 되고, 현위서기가 된 그는 서랍에 부치지 못한 첫 편지를 넣는다.</t>
-        </is>
-      </c>
-      <c r="F46" s="4" t="inlineStr">
-        <is>
-          <t>아버지 선궈칭, 기자 예란(실종), 쑤민의 변호사 자격</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>4부</t>
+          <t>1부</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>감옥 문 앞에서</t>
+          <t>법정의 각성</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>狱门之外</t>
+          <t>法庭的觉醒</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>7~11년(2021~2025년) / 선즈위안: 창촨시 시위서기 → 북원성 부성장 → 성장 / 쑤민: '잉훠' 조직자, 탕쉐의 공민 대리인 → 연금</t>
+          <t>0년(2014년) / 선즈위안·쑤민: 창촨시 한서우이 법률사무소의 젊은 변호사</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>쑤민 중심의 부. 광산 재개에 맞서다 다시 갇힌 탕쉐가 단식에 들어가고, 쑤민은 메이뤄란을 통해 부성장 선즈위안에게 '이송을 막지 마'라는 한 줄을 보낸다. 그의 전화는 하루 늦고 탕쉐는 옥중에서 숨진다. 빈 마을의 장례에서 두 번째로 마주친 두 사람 — '넌 안에서 무엇을 막았지?' 커팅웨가 진압을 멈추고 성위서기가 무너지지만, 성장 검증 면담에서 그는 쑤민과 '아무 관계 없다'고 답한다.</t>
+          <t>화학공장 폭발, 임금 체불, 폐수 오염, 산골 마을 강제 이주 사건을 스승 한서우이 아래서 나눠 맡으며 두 제자는 서로 다른 방식 — 조용한 증거 수집과 공개 탄원 — 을 익힌다. 커팅웨의 '차 마시자'는 호출 뒤 스승이 연행되어 숨지고, 두 사람은 스승의 찻잔 두 개를 하나씩 나눠 갖는다.</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>활동가 탕쉐(옥중 사망)</t>
+          <t>스승 한서우이</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>5부</t>
+          <t>2부</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>중앙으로</t>
+          <t>유리 너머</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>进京</t>
+          <t>隔着玻璃</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>12~17년(2026~2031년) / 선즈위안: 중앙위원·재정부장 → 정치국원 / 쑤민: 감시 속 '잉훠' 활동</t>
+          <t>0.5~1.5년(2015년) / 선즈위안·쑤민: 법률원조센터 '명등' 공동대표 → 선즈위안: 석방·입당 신청 / 쑤민: 구속·징역 3년</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>재정부장으로 베이징에 온 그는 공안 비밀 경비와 국유자본의 실소유 구조를 열어젖힌다. 희토류 수출 통제와 관세 전쟁 속에 서수이성이 반기를 들고, 정변 시도와 뤄전방의 몰락, 커팅웨의 퇴장이 이어진다. 구치소에서 숨진 가오밍저의 어머니가 쑤민을 찾아가고, 그녀가 받아 낸 부검 기록이 안쪽 수사의 단서가 된다 — 두 사람이 만나지 않고 함께 일한 첫 사건.</t>
+          <t>성도에서 '명등'을 연 두 사람은 돈의 유혹과 가족 압박, 탕쉐 사건을 함께 견디지만 어느 여름밤 함께 연행된다. 선즈위안은 아버지와 원로 간화이구의 탄원 끝에 '민감 사건 불수임' 보증서에 서명하고 나오고, 쑤민은 TV 자백을 거부하고 실형을 받는다. 입당 신청서를 품은 그가 접견실 유리 너머의 그녀를 만난다 — 첫 번째 만남, 갈라섬.</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>친구 가오밍저</t>
+          <t>동료 변호사들의 자유, 두 사람의 동행</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>6부</t>
+          <t>3부</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>정치국</t>
+          <t>안과 밖</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>政治局</t>
+          <t>里与外</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>17~18년(2031~2032년) / 선즈위안: 정치국원 → 총서기 / 쑤민: 압수수색과 '여행'을 견디는 '잉훠' 대표</t>
+          <t>1.5~6년(2015~2020년) / 선즈위안: 예비당원 → 칭허현 부현장(파견) → 현위서기 / 쑤민: 수감 → 출소(2018)·자격 박탈 → 지하 법률원조망 '잉훠' 조직</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>홀수 화는 쑤민. 웨이창펑 진영이 선즈위안의 과거를 치려고 쑤민에게 증언을 청하지만 그녀는 '나는 그를 비판하지만 당신들 도구는 아니다'라며 거절한다. 딥페이크, 감사팀 흔들기, 시찰장 폭발로 우슈전이 숨지고 청시가 다친다. 그녀는 '누가 이기든 지정거소를 없애라'는 손편지를 중앙위원들에게 보내고, 그는 첫 실질 경쟁 표결에서 총서기가 된다.</t>
+          <t>홀수 화는 감옥과 출소 뒤의 쑤민, 짝수 화는 '변절자' 선즈위안의 칭허현. 그가 융자플랫폼 부채와 토지 거래를 파헤치는 동안 아버지가 세상을 떠나고 예란이 사라지며, 그녀는 감방에서 상소장을 대신 쓰고 출소 뒤 자격 없이 지하 법률원조망 '잉훠'를 만든다. 메이뤄란이 두 사람 사이의 유일한 전령이 되고, 현위서기가 된 그는 서랍에 부치지 못한 첫 편지를 넣는다.</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>감사관 우슈전</t>
+          <t>아버지 선궈칭, 기자 예란(실종), 쑤민의 변호사 자격</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>7부</t>
+          <t>4부</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>무한의 유혹</t>
+          <t>감옥 문 앞에서</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>无限的诱惑</t>
+          <t>狱门之外</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>18~19년(2032~2033년), 총서기 1기 첫해 / 선즈위안: 총서기 / 쑤민: '청원 행동' 명단으로 지정거소감시거주</t>
+          <t>7~11년(2021~2025년) / 선즈위안: 창촨시 시위서기 → 북원성 부성장 → 성장 / 쑤민: '잉훠' 조직자, 탕쉐의 공민 대리인 → 연금</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>대홍수·지방채 연쇄부도·국경 긴장 속에서 사오톄쥔이 '청원 행동' 영도소조의 초법적 권한과 임기 제한 폐지를 내민다. 그가 결재한 '제한적' 통제안과 해외 연계 명단에 잉훠가 오르고, 쑤민이 총서기 이름의 공문으로 끌려간다. 청시와 정면으로 부딪친 뒤 지정거소 시설에서 세 번째로 그녀를 마주한 그는 벼랑 끝에서 전권을 내려놓는다.</t>
+          <t>쑤민 중심의 부. 광산 재개에 맞서다 다시 갇힌 탕쉐가 단식에 들어가고, 쑤민은 메이뤄란을 통해 부성장 선즈위안에게 '이송을 막지 마'라는 한 줄을 보낸다. 그의 전화는 하루 늦고 탕쉐는 옥중에서 숨진다. 빈 마을의 장례에서 두 번째로 마주친 두 사람 — '넌 안에서 무엇을 막았지?' 커팅웨가 진압을 멈추고 성위서기가 무너지지만, 성장 검증 면담에서 그는 쑤민과 '아무 관계 없다'고 답한다.</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>자기 확신(도덕적 상실), 그의 이름으로 빼앗은 쑤민의 자유</t>
+          <t>활동가 탕쉐(옥중 사망)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>8부</t>
+          <t>5부</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>권력의 경계</t>
+          <t>중앙으로</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>权力的边界</t>
+          <t>进京</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>19~22년(2033~2036년) / 선즈위안: 총서기(1기 후반~2기 초) / 쑤민: 석방 후 감시 속 '제자리 망명' 활동가</t>
+          <t>12~17년(2026~2031년) / 선즈위안: 중앙위원·재정부장 → 정치국원 / 쑤민: 감시 속 '잉훠' 활동</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>홀수 화는 쑤민. 그는 임기 2기 제한과 집체영도, 지정거소 제한에 더해 총서기 해임 절차를 직접 써 넣고, 청시는 그것을 '당신 자신에게 겨눈 총'이라 부른다. 쑤민은 메이뤄란이 가져온 초안을 빨간 펜으로 고쳐 보내면서도 정년 연장·연금 청원의 편에서 그의 정부를 공개 비판한다. 총공세 속에 정치밍이 쓰러지고, 패키지가 당장과 헌법에 확정되며, '차를 잊지 마'가 해독된다.</t>
+          <t>재정부장으로 베이징에 온 그는 공안 비밀 경비와 국유자본의 실소유 구조를 열어젖힌다. 희토류 수출 통제와 관세 전쟁 속에 서수이성이 반기를 들고, 정변 시도와 뤄전방의 몰락, 커팅웨의 퇴장이 이어진다. 구치소에서 숨진 가오밍저의 어머니가 쑤민을 찾아가고, 그녀가 받아 낸 부검 기록이 안쪽 수사의 단서가 된다 — 두 사람이 만나지 않고 함께 일한 첫 사건.</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>감사팀장 정치밍</t>
+          <t>친구 가오밍저</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>9부</t>
+          <t>6부</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>두 번째 임기</t>
+          <t>정치국</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>第二任期</t>
+          <t>政治局</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>22~27년(2036~2041년) / 선즈위안: 총서기(2기) / 쑤민: '사면 아닌 복권'을 요구하는 제자리 망명 활동가</t>
+          <t>17~18년(2031~2032년) / 선즈위안: 정치국원 → 총서기 / 쑤민: 압수수색과 '여행'을 견디는 '잉훠' 대표</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>2기 첫날 '5년 뒤 떠난다'고 공개 선언한 그는 낙인 조례를 폐지하지만, 사면 신청을 거부한 쑤민만은 복권 명단에서 빠진다. 서랍의 편지는 마흔 통이 되고, 커팅웨가 '규칙은 사람을 가리지 않는다, 당신도'라는 봉투를 남기고 숨진다. 청시가 공개 경쟁 추천으로 후계 후보가 되는 사이, 지방채 2차 위기와 '이 일은 당신만 끝낼 수 있다'는 측근들의 말이 쌓이고, 사오톄쥔이 '3기를 준비하자'고 속삭인다.</t>
+          <t>홀수 화는 쑤민. 웨이창펑 진영이 선즈위안의 과거를 치려고 쑤민에게 증언을 청하지만 그녀는 '나는 그를 비판하지만 당신들 도구는 아니다'라며 거절한다. 딥페이크, 감사팀 흔들기, 시찰장 폭발로 우슈전이 숨지고 청시가 다친다. 그녀는 '누가 이기든 지정거소를 없애라'는 손편지를 중앙위원들에게 보내고, 그는 첫 실질 경쟁 표결에서 총서기가 된다.</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>옛 적 커팅웨</t>
+          <t>감사관 우슈전</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
+          <t>7부</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>무한의 유혹</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>无限的诱惑</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>18~19년(2032~2033년), 총서기 1기 첫해 / 선즈위안: 총서기 / 쑤민: '청원 행동' 명단으로 지정거소감시거주</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>대홍수·지방채 연쇄부도·국경 긴장 속에서 사오톄쥔이 '청원 행동' 영도소조의 초법적 권한과 임기 제한 폐지를 내민다. 그가 결재한 '제한적' 통제안과 해외 연계 명단에 잉훠가 오르고, 쑤민이 총서기 이름의 공문으로 끌려간다. 청시와 정면으로 부딪친 뒤 지정거소 시설에서 세 번째로 그녀를 마주한 그는 벼랑 끝에서 전권을 내려놓는다.</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>자기 확신(도덕적 상실), 그의 이름으로 빼앗은 쑤민의 자유</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>8부</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>권력의 경계</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>权力的边界</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>19~22년(2033~2036년) / 선즈위안: 총서기(1기 후반~2기 초) / 쑤민: 석방 후 감시 속 '제자리 망명' 활동가</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>홀수 화는 쑤민. 그는 임기 2기 제한과 집체영도, 지정거소 제한에 더해 총서기 해임 절차를 직접 써 넣고, 청시는 그것을 '당신 자신에게 겨눈 총'이라 부른다. 쑤민은 메이뤄란이 가져온 초안을 빨간 펜으로 고쳐 보내면서도 정년 연장·연금 청원의 편에서 그의 정부를 공개 비판한다. 총공세 속에 정치밍이 쓰러지고, 패키지가 당장과 헌법에 확정되며, '차를 잊지 마'가 해독된다.</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>감사팀장 정치밍</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>9부</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>두 번째 임기</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>第二任期</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>22~27년(2036~2041년) / 선즈위안: 총서기(2기) / 쑤민: '사면 아닌 복권'을 요구하는 제자리 망명 활동가</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>2기 첫날 '5년 뒤 떠난다'고 공개 선언한 그는 낙인 조례를 폐지하지만, 사면 신청을 거부한 쑤민만은 복권 명단에서 빠진다. 서랍의 편지는 마흔 통이 되고, 커팅웨가 '규칙은 사람을 가리지 않는다, 당신도'라는 봉투를 남기고 숨진다. 청시가 공개 경쟁 추천으로 후계 후보가 되는 사이, 지방채 2차 위기와 '이 일은 당신만 끝낼 수 있다'는 측근들의 말이 쌓이고, 사오톄쥔이 '3기를 준비하자'고 속삭인다.</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>옛 적 커팅웨</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
           <t>10부</t>
         </is>
       </c>
-      <c r="B53" s="4" t="inlineStr">
+      <c r="B56" s="4" t="inlineStr">
         <is>
           <t>자기가 쓴 규칙</t>
         </is>
       </c>
-      <c r="C53" s="4" t="inlineStr">
+      <c r="C56" s="4" t="inlineStr">
         <is>
           <t>自己写的规则</t>
         </is>
       </c>
-      <c r="D53" s="4" t="inlineStr">
+      <c r="D56" s="4" t="inlineStr">
         <is>
           <t>27~28년(2041~2042년), 2기 마지막 해 / 에필로그 33년(2047년) / 선즈위안: 총서기(2기 마지막 해) → 해임된 평당원 / 쑤민: 연금 → 복권된 창구 변호사</t>
         </is>
       </c>
-      <c r="E53" s="4" t="inlineStr">
+      <c r="E56" s="4" t="inlineStr">
         <is>
           <t>대홍수와 지방은행 예금 동결 사태가 겹친 진짜 위기 속에서 간화이구가 '나가는 법을 보여 달라'는 말을 남기고 숨진다. 그는 '한 임기만 더'라는 측근들의 연임 요청 결의와 '영수' 호칭을 침묵으로 내버려 두고, 쑤민의 공개 서한은 다시 연금으로 돌아온다. 정치국원 3분의 1이 그가 쓴 해임 조항으로 동의안을 내고, 요양지에서 불려 온 그는 확대회의와 중앙위원회 표결을 변론 없이 받아들인다. 청시 지도부의 첫 결정은 쑤민의 복권이다.</t>
         </is>
       </c>
-      <c r="F53" s="4" t="inlineStr">
+      <c r="F56" s="4" t="inlineStr">
         <is>
           <t>입당 소개인 간화이구(병사), 권력, 그리고 '스스로 떠나는 사람'이라는 자기 서사</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="6" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr">
         <is>
           <t>4. 화별 구성</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="3" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
         <is>
           <t>부·화</t>
         </is>
       </c>
-      <c r="B56" s="3" t="inlineStr">
+      <c r="B59" s="3" t="inlineStr">
         <is>
           <t>제목(한국어)</t>
         </is>
       </c>
-      <c r="C56" s="3" t="inlineStr">
+      <c r="C59" s="3" t="inlineStr">
         <is>
           <t>제목(현지어)</t>
         </is>
       </c>
-      <c r="D56" s="3" t="inlineStr">
+      <c r="D59" s="3" t="inlineStr">
         <is>
           <t>대응 원작 화</t>
         </is>
       </c>
-      <c r="E56" s="3" t="inlineStr">
+      <c r="E59" s="3" t="inlineStr">
         <is>
           <t>한 줄 줄거리</t>
         </is>
       </c>
-      <c r="F56" s="3" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="4" t="inlineStr">
-        <is>
-          <t>1부 1화</t>
-        </is>
-      </c>
-      <c r="B57" s="4" t="inlineStr">
-        <is>
-          <t>첫 사건</t>
-        </is>
-      </c>
-      <c r="C57" s="4" t="inlineStr">
-        <is>
-          <t>第一个案子</t>
-        </is>
-      </c>
-      <c r="D57" s="4" t="inlineStr">
-        <is>
-          <t>1부 1화 변형</t>
-        </is>
-      </c>
-      <c r="E57" s="4" t="inlineStr">
-        <is>
-          <t>창촨 화학공장 폭발로 셋이 죽고 '조작 실수'로 종결된다. 한서우이는 유족에게 먼저 차를 따르고, 두 제자 선즈위안과 쑤민에게 사건을 나눠 맡긴다.</t>
-        </is>
-      </c>
-      <c r="F57" s="4" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="4" t="inlineStr">
-        <is>
-          <t>1부 2화</t>
-        </is>
-      </c>
-      <c r="B58" s="4" t="inlineStr">
-        <is>
-          <t>두 제자</t>
-        </is>
-      </c>
-      <c r="C58" s="4" t="inlineStr">
-        <is>
-          <t>两个徒弟</t>
-        </is>
-      </c>
-      <c r="D58" s="4" t="inlineStr">
-        <is>
-          <t>1부 2화 변형</t>
-        </is>
-      </c>
-      <c r="E58" s="4" t="inlineStr">
-        <is>
-          <t>노동자 설득은 선즈위안이, 서류 싸움은 쑤민이 맡는다. 두 사람은 스승이 1980년대 제방 고발 사건으로 자격을 잃었던 과거를 알게 된다.</t>
-        </is>
-      </c>
-      <c r="F58" s="4" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="4" t="inlineStr">
-        <is>
-          <t>1부 3화</t>
-        </is>
-      </c>
-      <c r="B59" s="4" t="inlineStr">
-        <is>
-          <t>회색지대</t>
-        </is>
-      </c>
-      <c r="C59" s="4" t="inlineStr">
-        <is>
-          <t>灰色地带</t>
-        </is>
-      </c>
-      <c r="D59" s="4" t="inlineStr">
-        <is>
-          <t>1부 3화 변형</t>
-        </is>
-      </c>
-      <c r="E59" s="4" t="inlineStr">
-        <is>
-          <t>국유 방직공장 여공들의 임금 체불. 뤄씨 그룹 법무대리가 합의금과 사내변호사 자리를 내밀자 선즈위안은 셈을 해 보고, 쑤민은 그 자리에서 거절한다.</t>
-        </is>
-      </c>
-      <c r="F59" s="4" t="inlineStr"/>
+      <c r="F59" s="3" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>1부 4화</t>
+          <t>1부 1화</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>첫 경고</t>
+          <t>첫 사건</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>第一次警告</t>
+          <t>第一个案子</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>1부 4화 변형</t>
+          <t>1부 1화 변형</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>파출소 민경이 선즈위안을 '차 한잔' 하자며 부르고, 같은 날 쑤민의 집주인은 이유 없이 임대 계약 해지를 통보한다.</t>
+          <t>창촨 화학공장 폭발로 셋이 죽고 '조작 실수'로 종결된다. 한서우이는 유족에게 먼저 차를 따르고, 두 제자 선즈위안과 쑤민에게 사건을 나눠 맡긴다.</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr"/>
@@ -11018,27 +10970,27 @@
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>1부 5화</t>
+          <t>1부 2화</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>작은 승리</t>
+          <t>두 제자</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>小胜利</t>
+          <t>两个徒弟</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>1부 5화</t>
+          <t>1부 2화 변형</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>염료공장 폐수로 썩은 마을 하천 사건에서 환경공익소송 첫 승소. 법정 밖에서 두 사람은 탐사기자 예란을 처음 만난다.</t>
+          <t>노동자 설득은 선즈위안이, 서류 싸움은 쑤민이 맡는다. 두 사람은 스승이 1980년대 제방 고발 사건으로 자격을 잃었던 과거를 알게 된다.</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr"/>
@@ -11046,27 +10998,27 @@
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>1부 6화</t>
+          <t>1부 3화</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>예란과의 인연</t>
+          <t>회색지대</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>与叶澜结缘</t>
+          <t>灰色地带</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>1부 6화</t>
+          <t>1부 3화 변형</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>예란이 공장 점검 비리 취재를 들고 정보 교환을 제안한다. 사무실 앞에는 번호판 없는 차가 서 있기 시작한다.</t>
+          <t>국유 방직공장 여공들의 임금 체불. 뤄씨 그룹 법무대리가 합의금과 사내변호사 자리를 내밀자 선즈위안은 셈을 해 보고, 쑤민은 그 자리에서 거절한다.</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr"/>
@@ -11074,27 +11026,27 @@
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>1부 7화</t>
+          <t>1부 4화</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>탕쉐의 등장</t>
+          <t>첫 경고</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>唐雪来了</t>
+          <t>第一次警告</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>1부 7화 변형</t>
+          <t>1부 4화 변형</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>희토류 광산을 위해 '생태이민'으로 산골 마을을 옮기려는 계획. 마을 교사 탕쉐가 문을 두드리고, 쑤민이 사건을 맡겠다고 나선다.</t>
+          <t>파출소 민경이 선즈위안을 '차 한잔' 하자며 부르고, 같은 날 쑤민의 집주인은 이유 없이 임대 계약 해지를 통보한다.</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr"/>
@@ -11102,27 +11054,27 @@
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>1부 8화</t>
+          <t>1부 5화</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>커팅웨의 그림자</t>
+          <t>작은 승리</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>柯庭岳的影子</t>
+          <t>小胜利</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>1부 8화</t>
+          <t>1부 5화</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>시 정법위 서기 커팅웨가 한서우이를 '차 마시자'고 부른다. 공손한 대화 끝에 남은 것은 두 제자의 이름이 적힌 분명한 경고다.</t>
+          <t>염료공장 폐수로 썩은 마을 하천 사건에서 환경공익소송 첫 승소. 법정 밖에서 두 사람은 탐사기자 예란을 처음 만난다.</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr"/>
@@ -11130,27 +11082,27 @@
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>1부 9화</t>
+          <t>1부 6화</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>한서우이 연행</t>
+          <t>예란과의 인연</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>韩守义被带走</t>
+          <t>与叶澜结缘</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>1부 9화</t>
+          <t>1부 6화</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>새벽, 한서우이가 '심흔자사' 혐의로 연행되어 지정거소감시거주에 들어간다. 가족도 변호인도 행방을 모른다.</t>
+          <t>예란이 공장 점검 비리 취재를 들고 정보 교환을 제안한다. 사무실 앞에는 번호판 없는 차가 서 있기 시작한다.</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr"/>
@@ -11158,27 +11110,27 @@
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>1부 10화</t>
+          <t>1부 7화</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>첫 갈림길</t>
+          <t>탕쉐의 등장</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>第一个岔路口</t>
+          <t>唐雪来了</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>1부 10화 변형</t>
+          <t>1부 7화 변형</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>심장약이 끊겼다는 소식. 쑤민은 실명 공개 탄원을 올리고, 선즈위안은 가오밍저를 통해 조용히 학대의 증거를 모은다. 서로를 못마땅해한다.</t>
+          <t>희토류 광산을 위해 '생태이민'으로 산골 마을을 옮기려는 계획. 마을 교사 탕쉐가 문을 두드리고, 쑤민이 사건을 맡겠다고 나선다.</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr"/>
@@ -11186,27 +11138,27 @@
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>1부 11화</t>
+          <t>1부 8화</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>한서우이의 죽음</t>
+          <t>커팅웨의 그림자</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>韩守义之死</t>
+          <t>柯庭岳的影子</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>1부 11화</t>
+          <t>1부 8화</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>외부의 관심에 밀려 취보후심으로 풀려난 한서우이가 나흘 만에 숨진다. 병원 기록에는 '지병'이라고만 적힌다.</t>
+          <t>시 정법위 서기 커팅웨가 한서우이를 '차 마시자'고 부른다. 공손한 대화 끝에 남은 것은 두 제자의 이름이 적힌 분명한 경고다.</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr"/>
@@ -11214,139 +11166,139 @@
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
+          <t>1부 9화</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>한서우이 연행</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>韩守义被带走</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>1부 9화</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>새벽, 한서우이가 '심흔자사' 혐의로 연행되어 지정거소감시거주에 들어간다. 가족도 변호인도 행방을 모른다.</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>1부 10화</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>첫 갈림길</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>第一个岔路口</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>1부 10화 변형</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>심장약이 끊겼다는 소식. 쑤민은 실명 공개 탄원을 올리고, 선즈위안은 가오밍저를 통해 조용히 학대의 증거를 모은다. 서로를 못마땅해한다.</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>1부 11화</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>한서우이의 죽음</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>韩守义之死</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>1부 11화</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>외부의 관심에 밀려 취보후심으로 풀려난 한서우이가 나흘 만에 숨진다. 병원 기록에는 '지병'이라고만 적힌다.</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
           <t>1부 12화</t>
         </is>
       </c>
-      <c r="B68" s="4" t="inlineStr">
+      <c r="B71" s="4" t="inlineStr">
         <is>
           <t>두 개의 찻잔</t>
         </is>
       </c>
-      <c r="C68" s="4" t="inlineStr">
+      <c r="C71" s="4" t="inlineStr">
         <is>
           <t>两只茶杯</t>
         </is>
       </c>
-      <c r="D68" s="4" t="inlineStr">
+      <c r="D71" s="4" t="inlineStr">
         <is>
           <t>1부 12화 변형</t>
         </is>
       </c>
-      <c r="E68" s="4" t="inlineStr">
+      <c r="E71" s="4" t="inlineStr">
         <is>
           <t>장례식에 그가 도운 사람들이 몰려든다. 두 제자는 나란히 조문객에게 차를 따르고, 스승의 찻잔 두 개를 하나씩 나눠 갖는다.</t>
         </is>
       </c>
-      <c r="F68" s="4" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="9" t="inlineStr">
-        <is>
-          <t>2부 1화</t>
-        </is>
-      </c>
-      <c r="B69" s="9" t="inlineStr">
-        <is>
-          <t>명등</t>
-        </is>
-      </c>
-      <c r="C69" s="9" t="inlineStr">
-        <is>
-          <t>明灯</t>
-        </is>
-      </c>
-      <c r="D69" s="9" t="inlineStr">
-        <is>
-          <t>2부 1화 변형</t>
-        </is>
-      </c>
-      <c r="E69" s="9" t="inlineStr">
-        <is>
-          <t>반년 뒤, 두 사람은 성도에 법률원조센터 '명등'을 함께 연다. 천장이 새는 방 두 칸에 자원활동가 리위퉁이 첫 손님으로 찾아온다.</t>
-        </is>
-      </c>
-      <c r="F69" s="9" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="9" t="inlineStr">
-        <is>
-          <t>2부 2화</t>
-        </is>
-      </c>
-      <c r="B70" s="9" t="inlineStr">
-        <is>
-          <t>돈의 유혹</t>
-        </is>
-      </c>
-      <c r="C70" s="9" t="inlineStr">
-        <is>
-          <t>金钱的诱惑</t>
-        </is>
-      </c>
-      <c r="D70" s="9" t="inlineStr">
-        <is>
-          <t>2부 2화</t>
-        </is>
-      </c>
-      <c r="E70" s="9" t="inlineStr">
-        <is>
-          <t>정체불명의 공익기금이 거액 후원을 제안한다. 리위퉁이 돈줄을 추적하자 뤄씨 그룹 계열사가 드러나고 센터는 거절한다.</t>
-        </is>
-      </c>
-      <c r="F70" s="9" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="9" t="inlineStr">
-        <is>
-          <t>2부 3화</t>
-        </is>
-      </c>
-      <c r="B71" s="9" t="inlineStr">
-        <is>
-          <t>예란의 특종</t>
-        </is>
-      </c>
-      <c r="C71" s="9" t="inlineStr">
-        <is>
-          <t>叶澜的独家</t>
-        </is>
-      </c>
-      <c r="D71" s="9" t="inlineStr">
-        <is>
-          <t>2부 3화</t>
-        </is>
-      </c>
-      <c r="E71" s="9" t="inlineStr">
-        <is>
-          <t>예란이 국유기업과 성 지도부의 유착 구조를 파헤치지만 기사는 게재 여섯 시간 만에 삭제되고 계정이 막힌다.</t>
-        </is>
-      </c>
-      <c r="F71" s="9" t="inlineStr"/>
+      <c r="F71" s="4" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="9" t="inlineStr">
         <is>
-          <t>2부 4화</t>
+          <t>2부 1화</t>
         </is>
       </c>
       <c r="B72" s="9" t="inlineStr">
         <is>
-          <t>법원 앞의 목소리</t>
+          <t>명등</t>
         </is>
       </c>
       <c r="C72" s="9" t="inlineStr">
         <is>
-          <t>法院门前的声音</t>
+          <t>明灯</t>
         </is>
       </c>
       <c r="D72" s="9" t="inlineStr">
         <is>
-          <t>2부 4화 변형</t>
+          <t>2부 1화 변형</t>
         </is>
       </c>
       <c r="E72" s="9" t="inlineStr">
         <is>
-          <t>집회가 불가능한 곳에서 쑤민이 피해자 가족들을 법원 앞에 조용히 세운다. 선즈위안은 '너무 빠르다'며 말리고, 연명은 하룻밤에 수만을 넘긴다.</t>
+          <t>반년 뒤, 두 사람은 성도에 법률원조센터 '명등'을 함께 연다. 천장이 새는 방 두 칸에 자원활동가 리위퉁이 첫 손님으로 찾아온다.</t>
         </is>
       </c>
       <c r="F72" s="9" t="inlineStr"/>
@@ -11354,27 +11306,27 @@
     <row r="73">
       <c r="A73" s="9" t="inlineStr">
         <is>
-          <t>2부 5화</t>
+          <t>2부 2화</t>
         </is>
       </c>
       <c r="B73" s="9" t="inlineStr">
         <is>
-          <t>가오밍저의 균열</t>
+          <t>돈의 유혹</t>
         </is>
       </c>
       <c r="C73" s="9" t="inlineStr">
         <is>
-          <t>高明哲的裂痕</t>
+          <t>金钱的诱惑</t>
         </is>
       </c>
       <c r="D73" s="9" t="inlineStr">
         <is>
-          <t>2부 5화</t>
+          <t>2부 2화</t>
         </is>
       </c>
       <c r="E73" s="9" t="inlineStr">
         <is>
-          <t>가오밍저의 로펌에 연례검사 탈락 위협이 떨어진다. 뤄씨 그룹 법무대리가 이번에는 직접 그를 찾아온다.</t>
+          <t>정체불명의 공익기금이 거액 후원을 제안한다. 리위퉁이 돈줄을 추적하자 뤄씨 그룹 계열사가 드러나고 센터는 거절한다.</t>
         </is>
       </c>
       <c r="F73" s="9" t="inlineStr"/>
@@ -11382,27 +11334,27 @@
     <row r="74">
       <c r="A74" s="9" t="inlineStr">
         <is>
-          <t>2부 6화</t>
+          <t>2부 3화</t>
         </is>
       </c>
       <c r="B74" s="9" t="inlineStr">
         <is>
-          <t>탕쉐의 구금</t>
+          <t>예란의 특종</t>
         </is>
       </c>
       <c r="C74" s="9" t="inlineStr">
         <is>
-          <t>唐雪被拘</t>
+          <t>叶澜的独家</t>
         </is>
       </c>
       <c r="D74" s="9" t="inlineStr">
         <is>
-          <t>2부 6화 변형</t>
+          <t>2부 3화</t>
         </is>
       </c>
       <c r="E74" s="9" t="inlineStr">
         <is>
-          <t>공사 중지 결정을 무시하고 중장비가 들어오자 탕쉐가 주민들과 길을 막고 '공공질서 교란'으로 구속된다. 쑤민이 변호인으로 선임된다.</t>
+          <t>예란이 국유기업과 성 지도부의 유착 구조를 파헤치지만 기사는 게재 여섯 시간 만에 삭제되고 계정이 막힌다.</t>
         </is>
       </c>
       <c r="F74" s="9" t="inlineStr"/>
@@ -11410,27 +11362,27 @@
     <row r="75">
       <c r="A75" s="9" t="inlineStr">
         <is>
-          <t>2부 7화</t>
+          <t>2부 4화</t>
         </is>
       </c>
       <c r="B75" s="9" t="inlineStr">
         <is>
-          <t>커팅웨의 제안</t>
+          <t>법원 앞의 목소리</t>
         </is>
       </c>
       <c r="C75" s="9" t="inlineStr">
         <is>
-          <t>柯庭岳的提议</t>
+          <t>法院门前的声音</t>
         </is>
       </c>
       <c r="D75" s="9" t="inlineStr">
         <is>
-          <t>2부 7화 변형</t>
+          <t>2부 4화 변형</t>
         </is>
       </c>
       <c r="E75" s="9" t="inlineStr">
         <is>
-          <t>커팅웨가 두 사람을 함께 부른다. 센터를 해산하면 탕쉐를 선처하겠다는 거래가 찻잔 위에 놓인다. 그는 망설이고, 그녀는 잔을 엎는다.</t>
+          <t>집회가 불가능한 곳에서 쑤민이 피해자 가족들을 법원 앞에 조용히 세운다. 선즈위안은 '너무 빠르다'며 말리고, 연명은 하룻밤에 수만을 넘긴다.</t>
         </is>
       </c>
       <c r="F75" s="9" t="inlineStr"/>
@@ -11438,27 +11390,27 @@
     <row r="76">
       <c r="A76" s="9" t="inlineStr">
         <is>
-          <t>2부 8화</t>
+          <t>2부 5화</t>
         </is>
       </c>
       <c r="B76" s="9" t="inlineStr">
         <is>
-          <t>마지막 같은 차</t>
+          <t>가오밍저의 균열</t>
         </is>
       </c>
       <c r="C76" s="9" t="inlineStr">
         <is>
-          <t>最后一杯同桌茶</t>
+          <t>高明哲的裂痕</t>
         </is>
       </c>
       <c r="D76" s="9" t="inlineStr">
         <is>
-          <t>2부 8화 변형</t>
+          <t>2부 5화</t>
         </is>
       </c>
       <c r="E76" s="9" t="inlineStr">
         <is>
-          <t>아버지의 연금과 당적이 조사받는 밤, 빈 사무실에서 두 사람은 '안에서 여는 문'과 '밖에서 두드리는 문'을 두고 처음으로 끝까지 다툰다.</t>
+          <t>가오밍저의 로펌에 연례검사 탈락 위협이 떨어진다. 뤄씨 그룹 법무대리가 이번에는 직접 그를 찾아온다.</t>
         </is>
       </c>
       <c r="F76" s="9" t="inlineStr"/>
@@ -11466,27 +11418,27 @@
     <row r="77">
       <c r="A77" s="9" t="inlineStr">
         <is>
-          <t>2부 9화</t>
+          <t>2부 6화</t>
         </is>
       </c>
       <c r="B77" s="9" t="inlineStr">
         <is>
-          <t>그 여름밤</t>
+          <t>탕쉐의 구금</t>
         </is>
       </c>
       <c r="C77" s="9" t="inlineStr">
         <is>
-          <t>那个夏夜</t>
+          <t>唐雪被拘</t>
         </is>
       </c>
       <c r="D77" s="9" t="inlineStr">
         <is>
-          <t>2부 9화 변형</t>
+          <t>2부 6화 변형</t>
         </is>
       </c>
       <c r="E77" s="9" t="inlineStr">
         <is>
-          <t>하룻밤 사이 전국의 동료 변호사 수십 명과 함께 두 사람도 연행된다. 지정거소의 서로 다른 방, 벽 너머에서 같은 질문이 반복된다.</t>
+          <t>공사 중지 결정을 무시하고 중장비가 들어오자 탕쉐가 주민들과 길을 막고 '공공질서 교란'으로 구속된다. 쑤민이 변호인으로 선임된다.</t>
         </is>
       </c>
       <c r="F77" s="9" t="inlineStr"/>
@@ -11494,27 +11446,27 @@
     <row r="78">
       <c r="A78" s="9" t="inlineStr">
         <is>
-          <t>2부 10화</t>
+          <t>2부 7화</t>
         </is>
       </c>
       <c r="B78" s="9" t="inlineStr">
         <is>
-          <t>보증서</t>
+          <t>커팅웨의 제안</t>
         </is>
       </c>
       <c r="C78" s="9" t="inlineStr">
         <is>
-          <t>保证书</t>
+          <t>柯庭岳的提议</t>
         </is>
       </c>
       <c r="D78" s="9" t="inlineStr">
         <is>
-          <t>신규</t>
+          <t>2부 7화 변형</t>
         </is>
       </c>
       <c r="E78" s="9" t="inlineStr">
         <is>
-          <t>아버지와 원로 간화이구의 탄원 끝에 선즈위안 앞에 '민감 사건 불수임' 보증서가 놓인다. 그는 서명하고 나온다. 아무에게도 말하지 않는다.</t>
+          <t>커팅웨가 두 사람을 함께 부른다. 센터를 해산하면 탕쉐를 선처하겠다는 거래가 찻잔 위에 놓인다. 그는 망설이고, 그녀는 잔을 엎는다.</t>
         </is>
       </c>
       <c r="F78" s="9" t="inlineStr"/>
@@ -11522,27 +11474,27 @@
     <row r="79">
       <c r="A79" s="9" t="inlineStr">
         <is>
-          <t>2부 11화</t>
+          <t>2부 8화</t>
         </is>
       </c>
       <c r="B79" s="9" t="inlineStr">
         <is>
-          <t>자백하지 않는 사람</t>
+          <t>마지막 같은 차</t>
         </is>
       </c>
       <c r="C79" s="9" t="inlineStr">
         <is>
-          <t>不认罪的人</t>
+          <t>最后一杯同桌茶</t>
         </is>
       </c>
       <c r="D79" s="9" t="inlineStr">
         <is>
-          <t>2부 11화 변형</t>
+          <t>2부 8화 변형</t>
         </is>
       </c>
       <c r="E79" s="9" t="inlineStr">
         <is>
-          <t>쑤민은 TV 자백을 끝내 거부하고 '국가정권 전복 선동'으로 징역 3년을 받는다. 같은 날 저녁 뉴스에는 동료 변호사의 '자백'이 방송된다.</t>
+          <t>아버지의 연금과 당적이 조사받는 밤, 빈 사무실에서 두 사람은 '안에서 여는 문'과 '밖에서 두드리는 문'을 두고 처음으로 끝까지 다툰다.</t>
         </is>
       </c>
       <c r="F79" s="9" t="inlineStr"/>
@@ -11550,139 +11502,139 @@
     <row r="80">
       <c r="A80" s="9" t="inlineStr">
         <is>
+          <t>2부 9화</t>
+        </is>
+      </c>
+      <c r="B80" s="9" t="inlineStr">
+        <is>
+          <t>그 여름밤</t>
+        </is>
+      </c>
+      <c r="C80" s="9" t="inlineStr">
+        <is>
+          <t>那个夏夜</t>
+        </is>
+      </c>
+      <c r="D80" s="9" t="inlineStr">
+        <is>
+          <t>2부 9화 변형</t>
+        </is>
+      </c>
+      <c r="E80" s="9" t="inlineStr">
+        <is>
+          <t>하룻밤 사이 전국의 동료 변호사 수십 명과 함께 두 사람도 연행된다. 지정거소의 서로 다른 방, 벽 너머에서 같은 질문이 반복된다.</t>
+        </is>
+      </c>
+      <c r="F80" s="9" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="9" t="inlineStr">
+        <is>
+          <t>2부 10화</t>
+        </is>
+      </c>
+      <c r="B81" s="9" t="inlineStr">
+        <is>
+          <t>보증서</t>
+        </is>
+      </c>
+      <c r="C81" s="9" t="inlineStr">
+        <is>
+          <t>保证书</t>
+        </is>
+      </c>
+      <c r="D81" s="9" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="E81" s="9" t="inlineStr">
+        <is>
+          <t>아버지와 원로 간화이구의 탄원 끝에 선즈위안 앞에 '민감 사건 불수임' 보증서가 놓인다. 그는 서명하고 나온다. 아무에게도 말하지 않는다.</t>
+        </is>
+      </c>
+      <c r="F81" s="9" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="9" t="inlineStr">
+        <is>
+          <t>2부 11화</t>
+        </is>
+      </c>
+      <c r="B82" s="9" t="inlineStr">
+        <is>
+          <t>자백하지 않는 사람</t>
+        </is>
+      </c>
+      <c r="C82" s="9" t="inlineStr">
+        <is>
+          <t>不认罪的人</t>
+        </is>
+      </c>
+      <c r="D82" s="9" t="inlineStr">
+        <is>
+          <t>2부 11화 변형</t>
+        </is>
+      </c>
+      <c r="E82" s="9" t="inlineStr">
+        <is>
+          <t>쑤민은 TV 자백을 끝내 거부하고 '국가정권 전복 선동'으로 징역 3년을 받는다. 같은 날 저녁 뉴스에는 동료 변호사의 '자백'이 방송된다.</t>
+        </is>
+      </c>
+      <c r="F82" s="9" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="9" t="inlineStr">
+        <is>
           <t>2부 12화</t>
         </is>
       </c>
-      <c r="B80" s="9" t="inlineStr">
+      <c r="B83" s="9" t="inlineStr">
         <is>
           <t>유리 너머</t>
         </is>
       </c>
-      <c r="C80" s="9" t="inlineStr">
+      <c r="C83" s="9" t="inlineStr">
         <is>
           <t>隔着玻璃</t>
         </is>
       </c>
-      <c r="D80" s="9" t="inlineStr">
+      <c r="D83" s="9" t="inlineStr">
         <is>
           <t>2부 12화 변형</t>
         </is>
       </c>
-      <c r="E80" s="9" t="inlineStr">
+      <c r="E83" s="9" t="inlineStr">
         <is>
           <t>첫 번째 만남. 입당 신청서를 품은 그가 간화이구의 주선으로 접견실에 앉는다. '안에서 열겠어.' '안에 들어가면 넌 그들의 말로 말하게 될 거야.'</t>
         </is>
       </c>
-      <c r="F80" s="9" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="4" t="inlineStr">
-        <is>
-          <t>3부 1화</t>
-        </is>
-      </c>
-      <c r="B81" s="4" t="inlineStr">
-        <is>
-          <t>감방의 법률</t>
-        </is>
-      </c>
-      <c r="C81" s="4" t="inlineStr">
-        <is>
-          <t>牢房里的法律</t>
-        </is>
-      </c>
-      <c r="D81" s="4" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="E81" s="4" t="inlineStr">
-        <is>
-          <t>[쑤민] 여자 교도소 감방에서 쑤민은 글을 모르는 수감자들의 상소장을 대신 써 준다. 펜이 압수되자 밥알로 종이를 붙여 쓴다. 감옥 안의 첫 법률원조.</t>
-        </is>
-      </c>
-      <c r="F81" s="4" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="4" t="inlineStr">
-        <is>
-          <t>3부 2화</t>
-        </is>
-      </c>
-      <c r="B82" s="4" t="inlineStr">
-        <is>
-          <t>선서</t>
-        </is>
-      </c>
-      <c r="C82" s="4" t="inlineStr">
-        <is>
-          <t>宣誓</t>
-        </is>
-      </c>
-      <c r="D82" s="4" t="inlineStr">
-        <is>
-          <t>3부 1화·2부 10화 변형</t>
-        </is>
-      </c>
-      <c r="E82" s="4" t="inlineStr">
-        <is>
-          <t>당기 앞에서 선서하는 날, 옛 동료들은 그를 '변절자'라 부르고 리위퉁만 곁에 남는다. 그날 밤 가오밍저가 찾아와 명등의 전략을 흘린 게 자기였다고 고백한다.</t>
-        </is>
-      </c>
-      <c r="F82" s="4" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="4" t="inlineStr">
-        <is>
-          <t>3부 3화</t>
-        </is>
-      </c>
-      <c r="B83" s="4" t="inlineStr">
-        <is>
-          <t>메이뤄란의 면회</t>
-        </is>
-      </c>
-      <c r="C83" s="4" t="inlineStr">
-        <is>
-          <t>梅若兰探监</t>
-        </is>
-      </c>
-      <c r="D83" s="4" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="E83" s="4" t="inlineStr">
-        <is>
-          <t>[쑤민] 스승의 오랜 벗 메이뤄란이 면회를 온다. '그 사람 소식은 전하지 마세요.' 면회가 끝날 무렵 쑤민이 먼저 묻는다. '잘 지내요?' 전령이 생긴다.</t>
-        </is>
-      </c>
-      <c r="F83" s="4" t="inlineStr"/>
+      <c r="F83" s="9" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>3부 4화</t>
+          <t>3부 1화</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>칭허현으로</t>
+          <t>감방의 법률</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>去青禾县</t>
+          <t>牢房里的法律</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>3부 3화 변형</t>
+          <t>신규</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>성의 전문인력 파견 실험으로 빈곤현 칭허의 부현장이 된다. 장부에 없는 융자플랫폼 부채와 짓다 만 아파트 단지가 기다린다.</t>
+          <t>[쑤민] 여자 교도소 감방에서 쑤민은 글을 모르는 수감자들의 상소장을 대신 써 준다. 펜이 압수되자 밥알로 종이를 붙여 쓴다. 감옥 안의 첫 법률원조.</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr"/>
@@ -11690,27 +11642,27 @@
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>3부 5화</t>
+          <t>3부 2화</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>탕쉐의 편지</t>
+          <t>선서</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>唐雪的信</t>
+          <t>宣誓</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>신규</t>
+          <t>3부 1화·2부 10화 변형</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>[쑤민] 다른 교도소의 탕쉐에게서 몰래 건너온 쪽지. 마을은 철거됐고 학교는 광산 사무소가 되었다. 쑤민은 출소하면 다시 그 사건을 맡겠다고 답한다.</t>
+          <t>당기 앞에서 선서하는 날, 옛 동료들은 그를 '변절자'라 부르고 리위퉁만 곁에 남는다. 그날 밤 가오밍저가 찾아와 명등의 전략을 흘린 게 자기였다고 고백한다.</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr"/>
@@ -11718,27 +11670,27 @@
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>3부 6화</t>
+          <t>3부 3화</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>아버지의 죽음</t>
+          <t>메이뤄란의 면회</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>父亲之死</t>
+          <t>梅若兰探监</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>3부 4화 변형</t>
+          <t>신규</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>아들을 자랑스러워한다는 아버지의 영상이 퍼진 뒤 아버지가 뇌졸중으로 쓰러진다. 그가 서명한 보증서를 아버지만은 알고 있었다.</t>
+          <t>[쑤민] 스승의 오랜 벗 메이뤄란이 면회를 온다. '그 사람 소식은 전하지 마세요.' 면회가 끝날 무렵 쑤민이 먼저 묻는다. '잘 지내요?' 전령이 생긴다.</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr"/>
@@ -11746,27 +11698,27 @@
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>3부 7화</t>
+          <t>3부 4화</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>출소</t>
+          <t>칭허현으로</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>出狱</t>
+          <t>去青禾县</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>신규</t>
+          <t>3부 3화 변형</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>[쑤민] 3년 만의 출소. 변호사 자격은 취소되고 출국은 금지되며, 집 앞엔 '보호' 요원이 선다. 어머니가 끓인 차 옆에 스승의 찻잔을 내려놓는다.</t>
+          <t>성의 전문인력 파견 실험으로 빈곤현 칭허의 부현장이 된다. 장부에 없는 융자플랫폼 부채와 짓다 만 아파트 단지가 기다린다.</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr"/>
@@ -11774,27 +11726,27 @@
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>3부 8화</t>
+          <t>3부 5화</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>예란의 실종</t>
+          <t>탕쉐의 편지</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>叶澜失踪</t>
+          <t>唐雪的信</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>3부 5·7화 변형</t>
+          <t>신규</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>칭허 토지 거래와 뤄씨 그룹을 잇는 예란의 기사가 공개되어 전국이 들끓는다. 그날 밤 그녀의 휴대전화가 꺼지고 돌아오지 않는다.</t>
+          <t>[쑤민] 다른 교도소의 탕쉐에게서 몰래 건너온 쪽지. 마을은 철거됐고 학교는 광산 사무소가 되었다. 쑤민은 출소하면 다시 그 사건을 맡겠다고 답한다.</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr"/>
@@ -11802,27 +11754,27 @@
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>3부 9화</t>
+          <t>3부 6화</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>잉훠</t>
+          <t>아버지의 죽음</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>萤火</t>
+          <t>父亲之死</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>신규</t>
+          <t>3부 4화 변형</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>[쑤민] 자격 없는 쑤민은 '공민 대리인'으로 첫 사건을 맡고, 출소한 동료들과 등록되지 않은 법률원조망 '잉훠'를 만든다. 간판 없는 이동 창구다.</t>
+          <t>아들을 자랑스러워한다는 아버지의 영상이 퍼진 뒤 아버지가 뇌졸중으로 쓰러진다. 그가 서명한 보증서를 아버지만은 알고 있었다.</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr"/>
@@ -11830,27 +11782,27 @@
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>3부 10화</t>
+          <t>3부 7화</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>가오밍저의 희생</t>
+          <t>출소</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>高明哲的牺牲</t>
+          <t>出狱</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>3부 9·10화 변형</t>
+          <t>신규</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>성 기율위가 그를 겨냥한 조사를 준비한다. 가오밍저가 장부 사본을 빼돌려 지키고 대신 유치 조사를 받는다. 커팅웨는 조사를 멈추며 셈을 남긴다.</t>
+          <t>[쑤민] 3년 만의 출소. 변호사 자격은 취소되고 출국은 금지되며, 집 앞엔 '보호' 요원이 선다. 어머니가 끓인 차 옆에 스승의 찻잔을 내려놓는다.</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr"/>
@@ -11858,27 +11810,27 @@
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>3부 11화</t>
+          <t>3부 8화</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>차 마시자</t>
+          <t>예란의 실종</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>喝茶</t>
+          <t>叶澜失踪</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>신규</t>
+          <t>3부 5·7화 변형</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>[쑤민] 출소 1년, 국보 요원이 쑤민을 '차 마시자'고 불러 잉훠 해산을 요구한다. 그녀는 찻잔에 손대지 않고, 이튿날 이동 창구를 다른 골목에 연다.</t>
+          <t>칭허 토지 거래와 뤄씨 그룹을 잇는 예란의 기사가 공개되어 전국이 들끓는다. 그날 밤 그녀의 휴대전화가 꺼지고 돌아오지 않는다.</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr"/>
@@ -11886,139 +11838,139 @@
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
+          <t>3부 9화</t>
+        </is>
+      </c>
+      <c r="B92" s="4" t="inlineStr">
+        <is>
+          <t>잉훠</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="inlineStr">
+        <is>
+          <t>萤火</t>
+        </is>
+      </c>
+      <c r="D92" s="4" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="E92" s="4" t="inlineStr">
+        <is>
+          <t>[쑤민] 자격 없는 쑤민은 '공민 대리인'으로 첫 사건을 맡고, 출소한 동료들과 등록되지 않은 법률원조망 '잉훠'를 만든다. 간판 없는 이동 창구다.</t>
+        </is>
+      </c>
+      <c r="F92" s="4" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>3부 10화</t>
+        </is>
+      </c>
+      <c r="B93" s="4" t="inlineStr">
+        <is>
+          <t>가오밍저의 희생</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t>高明哲的牺牲</t>
+        </is>
+      </c>
+      <c r="D93" s="4" t="inlineStr">
+        <is>
+          <t>3부 9·10화 변형</t>
+        </is>
+      </c>
+      <c r="E93" s="4" t="inlineStr">
+        <is>
+          <t>성 기율위가 그를 겨냥한 조사를 준비한다. 가오밍저가 장부 사본을 빼돌려 지키고 대신 유치 조사를 받는다. 커팅웨는 조사를 멈추며 셈을 남긴다.</t>
+        </is>
+      </c>
+      <c r="F93" s="4" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t>3부 11화</t>
+        </is>
+      </c>
+      <c r="B94" s="4" t="inlineStr">
+        <is>
+          <t>차 마시자</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="inlineStr">
+        <is>
+          <t>喝茶</t>
+        </is>
+      </c>
+      <c r="D94" s="4" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="E94" s="4" t="inlineStr">
+        <is>
+          <t>[쑤민] 출소 1년, 국보 요원이 쑤민을 '차 마시자'고 불러 잉훠 해산을 요구한다. 그녀는 찻잔에 손대지 않고, 이튿날 이동 창구를 다른 골목에 연다.</t>
+        </is>
+      </c>
+      <c r="F94" s="4" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="4" t="inlineStr">
+        <is>
           <t>3부 12화</t>
         </is>
       </c>
-      <c r="B92" s="4" t="inlineStr">
+      <c r="B95" s="4" t="inlineStr">
         <is>
           <t>공개된 장부</t>
         </is>
       </c>
-      <c r="C92" s="4" t="inlineStr">
+      <c r="C95" s="4" t="inlineStr">
         <is>
           <t>公开的账本</t>
         </is>
       </c>
-      <c r="D92" s="4" t="inlineStr">
+      <c r="D95" s="4" t="inlineStr">
         <is>
           <t>3부 11·12화 변형</t>
         </is>
       </c>
-      <c r="E92" s="4" t="inlineStr">
+      <c r="E95" s="4" t="inlineStr">
         <is>
           <t>현위서기가 된 그는 현 예산과 부채를 한 줄도 빼지 않은 '칭허 장부'를 공개한다. 그날 밤 서랍에 '쑤민에게'로 시작하는 첫 편지를 넣고 부치지 않는다.</t>
         </is>
       </c>
-      <c r="F92" s="4" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="9" t="inlineStr">
-        <is>
-          <t>4부 1화</t>
-        </is>
-      </c>
-      <c r="B93" s="9" t="inlineStr">
-        <is>
-          <t>공민 대리인</t>
-        </is>
-      </c>
-      <c r="C93" s="9" t="inlineStr">
-        <is>
-          <t>公民代理人</t>
-        </is>
-      </c>
-      <c r="D93" s="9" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="E93" s="9" t="inlineStr">
-        <is>
-          <t>[쑤민] 형기를 마치고도 광산 재개에 맞서던 탕쉐가 다시 구속된다. 법정 출입증도 없는 쑤민이 '공민 대리인'으로 변론석에 앉는다.</t>
-        </is>
-      </c>
-      <c r="F93" s="9" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="9" t="inlineStr">
-        <is>
-          <t>4부 2화</t>
-        </is>
-      </c>
-      <c r="B94" s="9" t="inlineStr">
-        <is>
-          <t>고향의 시위서기</t>
-        </is>
-      </c>
-      <c r="C94" s="9" t="inlineStr">
-        <is>
-          <t>家乡的市委书记</t>
-        </is>
-      </c>
-      <c r="D94" s="9" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="E94" s="9" t="inlineStr">
-        <is>
-          <t>창촨시 시위서기로 고향에 돌아온 그는 1부의 폭발 공장을 품은 화학단지를 주거지 밖으로 옮기는 결정을 내린다. 박수는 크다.</t>
-        </is>
-      </c>
-      <c r="F94" s="9" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="9" t="inlineStr">
-        <is>
-          <t>4부 3화</t>
-        </is>
-      </c>
-      <c r="B95" s="9" t="inlineStr">
-        <is>
-          <t>옥중 단식</t>
-        </is>
-      </c>
-      <c r="C95" s="9" t="inlineStr">
-        <is>
-          <t>狱中绝食</t>
-        </is>
-      </c>
-      <c r="D95" s="9" t="inlineStr">
-        <is>
-          <t>4부 2화 변형</t>
-        </is>
-      </c>
-      <c r="E95" s="9" t="inlineStr">
-        <is>
-          <t>[쑤민] 탕쉐가 단식에 들어간다. 면회실 유리 너머로 그녀는 웃는다. 쑤민은 메이뤄란 편에 그에게 한 줄을 보낸다. '이송을 막지 마.'</t>
-        </is>
-      </c>
-      <c r="F95" s="9" t="inlineStr"/>
+      <c r="F95" s="4" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="9" t="inlineStr">
         <is>
-          <t>4부 4화</t>
+          <t>4부 1화</t>
         </is>
       </c>
       <c r="B96" s="9" t="inlineStr">
         <is>
-          <t>부성장과 청시</t>
+          <t>공민 대리인</t>
         </is>
       </c>
       <c r="C96" s="9" t="inlineStr">
         <is>
-          <t>副省长与程曦</t>
+          <t>公民代理人</t>
         </is>
       </c>
       <c r="D96" s="9" t="inlineStr">
         <is>
-          <t>4부 1·3화 변형</t>
+          <t>신규</t>
         </is>
       </c>
       <c r="E96" s="9" t="inlineStr">
         <is>
-          <t>개발사 연쇄 부도의 해, 그는 부성장으로 발탁되고 스물두 살 선조생 청시가 첫날부터 보고서의 숫자가 틀렸다고 지적한다. 메이뤄란의 전언은 서류 더미 아래 놓인다.</t>
+          <t>[쑤민] 형기를 마치고도 광산 재개에 맞서던 탕쉐가 다시 구속된다. 법정 출입증도 없는 쑤민이 '공민 대리인'으로 변론석에 앉는다.</t>
         </is>
       </c>
       <c r="F96" s="9" t="inlineStr"/>
@@ -12026,27 +11978,27 @@
     <row r="97">
       <c r="A97" s="9" t="inlineStr">
         <is>
-          <t>4부 5화</t>
+          <t>4부 2화</t>
         </is>
       </c>
       <c r="B97" s="9" t="inlineStr">
         <is>
-          <t>호송 절차</t>
+          <t>고향의 시위서기</t>
         </is>
       </c>
       <c r="C97" s="9" t="inlineStr">
         <is>
-          <t>押送程序</t>
+          <t>家乡的市委书记</t>
         </is>
       </c>
       <c r="D97" s="9" t="inlineStr">
         <is>
-          <t>4부 5화 변형</t>
+          <t>신규</t>
         </is>
       </c>
       <c r="E97" s="9" t="inlineStr">
         <is>
-          <t>[쑤민] 법원이 병원 이송을 허가하지만 '호송 절차'로 하루가 지연된다. 쑤민은 교도소 정문 앞에서 밤을 새우고, 그의 전화는 다음 날 아침에야 걸린다.</t>
+          <t>창촨시 시위서기로 고향에 돌아온 그는 1부의 폭발 공장을 품은 화학단지를 주거지 밖으로 옮기는 결정을 내린다. 박수는 크다.</t>
         </is>
       </c>
       <c r="F97" s="9" t="inlineStr"/>
@@ -12054,27 +12006,27 @@
     <row r="98">
       <c r="A98" s="9" t="inlineStr">
         <is>
-          <t>4부 6화</t>
+          <t>4부 3화</t>
         </is>
       </c>
       <c r="B98" s="9" t="inlineStr">
         <is>
-          <t>탕쉐의 죽음</t>
+          <t>옥중 단식</t>
         </is>
       </c>
       <c r="C98" s="9" t="inlineStr">
         <is>
-          <t>唐雪之死</t>
+          <t>狱中绝食</t>
         </is>
       </c>
       <c r="D98" s="9" t="inlineStr">
         <is>
-          <t>4부 5화 변형</t>
+          <t>4부 2화 변형</t>
         </is>
       </c>
       <c r="E98" s="9" t="inlineStr">
         <is>
-          <t>단식 14일째, 탕쉐가 교도소에서 숨진다. 선즈위안은 통화 기록을 보며 자신이 '절차대로' 하루를 기다렸다는 사실과 마주한다.</t>
+          <t>[쑤민] 탕쉐가 단식에 들어간다. 면회실 유리 너머로 그녀는 웃는다. 쑤민은 메이뤄란 편에 그에게 한 줄을 보낸다. '이송을 막지 마.'</t>
         </is>
       </c>
       <c r="F98" s="9" t="inlineStr"/>
@@ -12082,27 +12034,27 @@
     <row r="99">
       <c r="A99" s="9" t="inlineStr">
         <is>
-          <t>4부 7화</t>
+          <t>4부 4화</t>
         </is>
       </c>
       <c r="B99" s="9" t="inlineStr">
         <is>
-          <t>두 번째 만남</t>
+          <t>부성장과 청시</t>
         </is>
       </c>
       <c r="C99" s="9" t="inlineStr">
         <is>
-          <t>第二次见面</t>
+          <t>副省长与程曦</t>
         </is>
       </c>
       <c r="D99" s="9" t="inlineStr">
         <is>
-          <t>4부 6화 변형</t>
+          <t>4부 1·3화 변형</t>
         </is>
       </c>
       <c r="E99" s="9" t="inlineStr">
         <is>
-          <t>빈 마을에서 치러진 장례. 조문 행렬 속에서 두 사람이 마주친다. '넌 안에서 무엇을 막았지?' 그는 답하지 못하고, 그녀는 먼저 등을 돌린다.</t>
+          <t>개발사 연쇄 부도의 해, 그는 부성장으로 발탁되고 스물두 살 선조생 청시가 첫날부터 보고서의 숫자가 틀렸다고 지적한다. 메이뤄란의 전언은 서류 더미 아래 놓인다.</t>
         </is>
       </c>
       <c r="F99" s="9" t="inlineStr"/>
@@ -12110,27 +12062,27 @@
     <row r="100">
       <c r="A100" s="9" t="inlineStr">
         <is>
-          <t>4부 8화</t>
+          <t>4부 5화</t>
         </is>
       </c>
       <c r="B100" s="9" t="inlineStr">
         <is>
-          <t>커팅웨의 선택</t>
+          <t>호송 절차</t>
         </is>
       </c>
       <c r="C100" s="9" t="inlineStr">
         <is>
-          <t>柯庭岳的选择</t>
+          <t>押送程序</t>
         </is>
       </c>
       <c r="D100" s="9" t="inlineStr">
         <is>
-          <t>4부 6·7화 변형</t>
+          <t>4부 5화 변형</t>
         </is>
       </c>
       <c r="E100" s="9" t="inlineStr">
         <is>
-          <t>조문 행렬이 여러 도시로 번지자 성 긴급 회의에 무장경찰 투입안이 오른다. 커팅웨는 35년 만에 처음으로 명령서에 서명하지 않는다.</t>
+          <t>[쑤민] 법원이 병원 이송을 허가하지만 '호송 절차'로 하루가 지연된다. 쑤민은 교도소 정문 앞에서 밤을 새우고, 그의 전화는 다음 날 아침에야 걸린다.</t>
         </is>
       </c>
       <c r="F100" s="9" t="inlineStr"/>
@@ -12138,27 +12090,27 @@
     <row r="101">
       <c r="A101" s="9" t="inlineStr">
         <is>
-          <t>4부 9화</t>
+          <t>4부 6화</t>
         </is>
       </c>
       <c r="B101" s="9" t="inlineStr">
         <is>
-          <t>지워지는 이름</t>
+          <t>탕쉐의 죽음</t>
         </is>
       </c>
       <c r="C101" s="9" t="inlineStr">
         <is>
-          <t>被删除的名字</t>
+          <t>唐雪之死</t>
         </is>
       </c>
       <c r="D101" s="9" t="inlineStr">
         <is>
-          <t>신규</t>
+          <t>4부 5화 변형</t>
         </is>
       </c>
       <c r="E101" s="9" t="inlineStr">
         <is>
-          <t>[쑤민] 탕쉐의 추모 글이 지워지고 쑤민은 아파트에 연금된다. 잉훠 동료들이 탕쉐의 단식 기록을 해외 서버에 하나씩 옮겨 보존한다.</t>
+          <t>단식 14일째, 탕쉐가 교도소에서 숨진다. 선즈위안은 통화 기록을 보며 자신이 '절차대로' 하루를 기다렸다는 사실과 마주한다.</t>
         </is>
       </c>
       <c r="F101" s="9" t="inlineStr"/>
@@ -12166,27 +12118,27 @@
     <row r="102">
       <c r="A102" s="9" t="inlineStr">
         <is>
-          <t>4부 10화</t>
+          <t>4부 7화</t>
         </is>
       </c>
       <c r="B102" s="9" t="inlineStr">
         <is>
-          <t>제후의 낙마</t>
+          <t>두 번째 만남</t>
         </is>
       </c>
       <c r="C102" s="9" t="inlineStr">
         <is>
-          <t>封疆大吏落马</t>
+          <t>第二次见面</t>
         </is>
       </c>
       <c r="D102" s="9" t="inlineStr">
         <is>
-          <t>4부 4·9화 변형</t>
+          <t>4부 6화 변형</t>
         </is>
       </c>
       <c r="E102" s="9" t="inlineStr">
         <is>
-          <t>광산을 대가로 내민 뤄전방의 손을 뿌리치자 감사팀의 자금 흐름과 커팅웨의 통화 기록이 중앙기율위에 닿고, 성위서기 펑치산이 회의 도중 연행된다.</t>
+          <t>빈 마을에서 치러진 장례. 조문 행렬 속에서 두 사람이 마주친다. '넌 안에서 무엇을 막았지?' 그는 답하지 못하고, 그녀는 먼저 등을 돌린다.</t>
         </is>
       </c>
       <c r="F102" s="9" t="inlineStr"/>
@@ -12194,27 +12146,27 @@
     <row r="103">
       <c r="A103" s="9" t="inlineStr">
         <is>
-          <t>4부 11화</t>
+          <t>4부 8화</t>
         </is>
       </c>
       <c r="B103" s="9" t="inlineStr">
         <is>
-          <t>옥중 사망 보고서</t>
+          <t>커팅웨의 선택</t>
         </is>
       </c>
       <c r="C103" s="9" t="inlineStr">
         <is>
-          <t>狱中死亡报告</t>
+          <t>柯庭岳的选择</t>
         </is>
       </c>
       <c r="D103" s="9" t="inlineStr">
         <is>
-          <t>신규</t>
+          <t>4부 6·7화 변형</t>
         </is>
       </c>
       <c r="E103" s="9" t="inlineStr">
         <is>
-          <t>[쑤민] 연금된 방에서 쑤민은 탕쉐의 진술을 정리해 '옥중 사망 보고서'를 낸다. 성 정부의 답신 서명란에는 대리성장 선즈위안의 이름이 찍혀 있다.</t>
+          <t>조문 행렬이 여러 도시로 번지자 성 긴급 회의에 무장경찰 투입안이 오른다. 커팅웨는 35년 만에 처음으로 명령서에 서명하지 않는다.</t>
         </is>
       </c>
       <c r="F103" s="9" t="inlineStr"/>
@@ -12222,139 +12174,139 @@
     <row r="104">
       <c r="A104" s="9" t="inlineStr">
         <is>
+          <t>4부 9화</t>
+        </is>
+      </c>
+      <c r="B104" s="9" t="inlineStr">
+        <is>
+          <t>지워지는 이름</t>
+        </is>
+      </c>
+      <c r="C104" s="9" t="inlineStr">
+        <is>
+          <t>被删除的名字</t>
+        </is>
+      </c>
+      <c r="D104" s="9" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="E104" s="9" t="inlineStr">
+        <is>
+          <t>[쑤민] 탕쉐의 추모 글이 지워지고 쑤민은 아파트에 연금된다. 잉훠 동료들이 탕쉐의 단식 기록을 해외 서버에 하나씩 옮겨 보존한다.</t>
+        </is>
+      </c>
+      <c r="F104" s="9" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="9" t="inlineStr">
+        <is>
+          <t>4부 10화</t>
+        </is>
+      </c>
+      <c r="B105" s="9" t="inlineStr">
+        <is>
+          <t>제후의 낙마</t>
+        </is>
+      </c>
+      <c r="C105" s="9" t="inlineStr">
+        <is>
+          <t>封疆大吏落马</t>
+        </is>
+      </c>
+      <c r="D105" s="9" t="inlineStr">
+        <is>
+          <t>4부 4·9화 변형</t>
+        </is>
+      </c>
+      <c r="E105" s="9" t="inlineStr">
+        <is>
+          <t>광산을 대가로 내민 뤄전방의 손을 뿌리치자 감사팀의 자금 흐름과 커팅웨의 통화 기록이 중앙기율위에 닿고, 성위서기 펑치산이 회의 도중 연행된다.</t>
+        </is>
+      </c>
+      <c r="F105" s="9" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="9" t="inlineStr">
+        <is>
+          <t>4부 11화</t>
+        </is>
+      </c>
+      <c r="B106" s="9" t="inlineStr">
+        <is>
+          <t>옥중 사망 보고서</t>
+        </is>
+      </c>
+      <c r="C106" s="9" t="inlineStr">
+        <is>
+          <t>狱中死亡报告</t>
+        </is>
+      </c>
+      <c r="D106" s="9" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="E106" s="9" t="inlineStr">
+        <is>
+          <t>[쑤민] 연금된 방에서 쑤민은 탕쉐의 진술을 정리해 '옥중 사망 보고서'를 낸다. 성 정부의 답신 서명란에는 대리성장 선즈위안의 이름이 찍혀 있다.</t>
+        </is>
+      </c>
+      <c r="F106" s="9" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="9" t="inlineStr">
+        <is>
           <t>4부 12화</t>
         </is>
       </c>
-      <c r="B104" s="9" t="inlineStr">
+      <c r="B107" s="9" t="inlineStr">
         <is>
           <t>아무 관계 없다</t>
         </is>
       </c>
-      <c r="C104" s="9" t="inlineStr">
+      <c r="C107" s="9" t="inlineStr">
         <is>
           <t>毫无关系</t>
         </is>
       </c>
-      <c r="D104" s="9" t="inlineStr">
+      <c r="D107" s="9" t="inlineStr">
         <is>
           <t>4부 10·11·12화 변형</t>
         </is>
       </c>
-      <c r="E104" s="9" t="inlineStr">
+      <c r="E107" s="9" t="inlineStr">
         <is>
           <t>성장 임명을 앞둔 조직부 검증 면담. '쑤민과의 관계는?' '아무 관계 없습니다.' 그날 밤 그는 한서우이·아버지·탕쉐의 무덤을 차례로 찾는다.</t>
         </is>
       </c>
-      <c r="F104" s="9" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="4" t="inlineStr">
-        <is>
-          <t>5부 1화</t>
-        </is>
-      </c>
-      <c r="B105" s="4" t="inlineStr">
-        <is>
-          <t>베이징의 첫 벽</t>
-        </is>
-      </c>
-      <c r="C105" s="4" t="inlineStr">
-        <is>
-          <t>北京的第一堵墙</t>
-        </is>
-      </c>
-      <c r="D105" s="4" t="inlineStr">
-        <is>
-          <t>5부 1화</t>
-        </is>
-      </c>
-      <c r="E105" s="4" t="inlineStr">
-        <is>
-          <t>중앙위원 겸 재정부장이 되자 예비비 자료가 나오지 않는다. 부부장 구옌자오는 '1년 안에 당신은 여기 없을 것'이라 말한다.</t>
-        </is>
-      </c>
-      <c r="F105" s="4" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="4" t="inlineStr">
-        <is>
-          <t>5부 2화</t>
-        </is>
-      </c>
-      <c r="B106" s="4" t="inlineStr">
-        <is>
-          <t>커팅웨와의 새 계약</t>
-        </is>
-      </c>
-      <c r="C106" s="4" t="inlineStr">
-        <is>
-          <t>与柯庭岳的新契约</t>
-        </is>
-      </c>
-      <c r="D106" s="4" t="inlineStr">
-        <is>
-          <t>5부 2화</t>
-        </is>
-      </c>
-      <c r="E106" s="4" t="inlineStr">
-        <is>
-          <t>예비비 감사가 공안 계통의 '특수 경비'로 이어진다. 중앙 정법 계통으로 올라간 커팅웨와 다시 마주 앉는다.</t>
-        </is>
-      </c>
-      <c r="F106" s="4" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="4" t="inlineStr">
-        <is>
-          <t>5부 3화</t>
-        </is>
-      </c>
-      <c r="B107" s="4" t="inlineStr">
-        <is>
-          <t>뤄전방의 마지막 패</t>
-        </is>
-      </c>
-      <c r="C107" s="4" t="inlineStr">
-        <is>
-          <t>骆振邦的最后一张牌</t>
-        </is>
-      </c>
-      <c r="D107" s="4" t="inlineStr">
-        <is>
-          <t>5부 3화</t>
-        </is>
-      </c>
-      <c r="E107" s="4" t="inlineStr">
-        <is>
-          <t>국유자본 실소유자 공개 조례가 뤄전방의 제국을 겨눈다. 그는 원로 아버지의 인맥을 총동원해 반격한다.</t>
-        </is>
-      </c>
-      <c r="F107" s="4" t="inlineStr"/>
+      <c r="F107" s="9" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>5부 4화</t>
+          <t>5부 1화</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>변방의 반기</t>
+          <t>베이징의 첫 벽</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>边疆的反旗</t>
+          <t>北京的第一堵墙</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>5부 4화</t>
+          <t>5부 1화</t>
         </is>
       </c>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t>수출 통제로 협상 카드가 된 희토류 산지 서수이성의 서기가 '특구' 명목으로 공개 조례를 거부한다. 부성장 녜추가 숨은 장부를 들고 온다.</t>
+          <t>중앙위원 겸 재정부장이 되자 예비비 자료가 나오지 않는다. 부부장 구옌자오는 '1년 안에 당신은 여기 없을 것'이라 말한다.</t>
         </is>
       </c>
       <c r="F108" s="4" t="inlineStr"/>
@@ -12362,27 +12314,27 @@
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>5부 5화</t>
+          <t>5부 2화</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>개혁의 대가</t>
+          <t>커팅웨와의 새 계약</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>改革的代价</t>
+          <t>与柯庭岳的新契约</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>5부 5화</t>
+          <t>5부 2화</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>사법 부패망 조사에 자원한 가오밍저가 구치소에서 숨진 채 발견된다. 공식 발표는 '자살'이다.</t>
+          <t>예비비 감사가 공안 계통의 '특수 경비'로 이어진다. 중앙 정법 계통으로 올라간 커팅웨와 다시 마주 앉는다.</t>
         </is>
       </c>
       <c r="F109" s="4" t="inlineStr"/>
@@ -12390,27 +12342,27 @@
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>5부 6화</t>
+          <t>5부 3화</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>가오밍저의 어머니</t>
+          <t>뤄전방의 마지막 패</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>高明哲的母亲</t>
+          <t>骆振邦的最后一张牌</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>신규</t>
+          <t>5부 3화</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
-          <t>[쑤민] 아들의 부검을 요구하던 가오밍저의 어머니가 모든 로펌에서 거절당한 끝에 잉훠의 골목 창구를 찾아온다. 쑤민이 사건을 맡는다.</t>
+          <t>국유자본 실소유자 공개 조례가 뤄전방의 제국을 겨눈다. 그는 원로 아버지의 인맥을 총동원해 반격한다.</t>
         </is>
       </c>
       <c r="F110" s="4" t="inlineStr"/>
@@ -12418,27 +12370,27 @@
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>5부 7화</t>
+          <t>5부 4화</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>정변 미수</t>
+          <t>변방의 반기</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>未遂的政变</t>
+          <t>边疆的反旗</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>5부 6·7화 변형</t>
+          <t>5부 4화</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>관세 전쟁과 자본 이탈로 개혁 비난이 커지는 사이, 기율위 조사를 앞둔 정법계 강경파가 새벽에 무장경찰을 움직인다. 가장 긴 밤.</t>
+          <t>수출 통제로 협상 카드가 된 희토류 산지 서수이성의 서기가 '특구' 명목으로 공개 조례를 거부한다. 부성장 녜추가 숨은 장부를 들고 온다.</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr"/>
@@ -12446,27 +12398,27 @@
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t>5부 8화</t>
+          <t>5부 5화</t>
         </is>
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>뤄전방의 몰락</t>
+          <t>개혁의 대가</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>骆振邦的倒台</t>
+          <t>改革的代价</t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>5부 8화</t>
+          <t>5부 5화</t>
         </is>
       </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>마지막 은닉 구조가 드러나고 뤄전방은 공항 출국 심사대 앞에서 연행된다. 원로의 전화는 끝내 오지 않는다.</t>
+          <t>사법 부패망 조사에 자원한 가오밍저가 구치소에서 숨진 채 발견된다. 공식 발표는 '자살'이다.</t>
         </is>
       </c>
       <c r="F112" s="4" t="inlineStr"/>
@@ -12474,27 +12426,27 @@
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>5부 9화</t>
+          <t>5부 6화</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>커팅웨의 퇴장</t>
+          <t>가오밍저의 어머니</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>柯庭岳退场</t>
+          <t>高明哲的母亲</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>5부 9화 변형</t>
+          <t>신규</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>쑤민이 받아 낸 부검 기록이 메이뤄란을 거쳐 그의 책상에 닿는다. 살해 자금은 예란 실종 당일의 송금 사슬과 겹치고, 커팅웨가 사직서를 낸다.</t>
+          <t>[쑤민] 아들의 부검을 요구하던 가오밍저의 어머니가 모든 로펌에서 거절당한 끝에 잉훠의 골목 창구를 찾아온다. 쑤민이 사건을 맡는다.</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr"/>
@@ -12502,27 +12454,27 @@
     <row r="114">
       <c r="A114" s="4" t="inlineStr">
         <is>
-          <t>5부 10화</t>
+          <t>5부 7화</t>
         </is>
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>전체회의</t>
+          <t>정변 미수</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>全会</t>
+          <t>未遂的政变</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>5부 10화</t>
+          <t>5부 6·7화 변형</t>
         </is>
       </c>
       <c r="E114" s="4" t="inlineStr">
         <is>
-          <t>재정 공개와 사법 독립을 묶은 중앙위원회 결의가 표결에 오른다. 그가 스스로 넣은 자기 심사 조항도 함께다.</t>
+          <t>관세 전쟁과 자본 이탈로 개혁 비난이 커지는 사이, 기율위 조사를 앞둔 정법계 강경파가 새벽에 무장경찰을 움직인다. 가장 긴 밤.</t>
         </is>
       </c>
       <c r="F114" s="4" t="inlineStr"/>
@@ -12530,27 +12482,27 @@
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>5부 11화</t>
+          <t>5부 8화</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>탕핑 세대</t>
+          <t>뤄전방의 몰락</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>躺平的一代</t>
+          <t>骆振邦的倒台</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>5부 11화 변형</t>
+          <t>5부 8화</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>[쑤민] 청년 실업 속 배달 기사들의 임금 소송에 잉훠의 젊은 자원활동가들이 몰린다. 쑤민은 '안의 개혁'이 이 골목엔 아직 오지 않았다고 쓴다.</t>
+          <t>마지막 은닉 구조가 드러나고 뤄전방은 공항 출국 심사대 앞에서 연행된다. 원로의 전화는 끝내 오지 않는다.</t>
         </is>
       </c>
       <c r="F115" s="4" t="inlineStr"/>
@@ -12558,139 +12510,139 @@
     <row r="116">
       <c r="A116" s="4" t="inlineStr">
         <is>
+          <t>5부 9화</t>
+        </is>
+      </c>
+      <c r="B116" s="4" t="inlineStr">
+        <is>
+          <t>커팅웨의 퇴장</t>
+        </is>
+      </c>
+      <c r="C116" s="4" t="inlineStr">
+        <is>
+          <t>柯庭岳退场</t>
+        </is>
+      </c>
+      <c r="D116" s="4" t="inlineStr">
+        <is>
+          <t>5부 9화 변형</t>
+        </is>
+      </c>
+      <c r="E116" s="4" t="inlineStr">
+        <is>
+          <t>쑤민이 받아 낸 부검 기록이 메이뤄란을 거쳐 그의 책상에 닿는다. 살해 자금은 예란 실종 당일의 송금 사슬과 겹치고, 커팅웨가 사직서를 낸다.</t>
+        </is>
+      </c>
+      <c r="F116" s="4" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="4" t="inlineStr">
+        <is>
+          <t>5부 10화</t>
+        </is>
+      </c>
+      <c r="B117" s="4" t="inlineStr">
+        <is>
+          <t>전체회의</t>
+        </is>
+      </c>
+      <c r="C117" s="4" t="inlineStr">
+        <is>
+          <t>全会</t>
+        </is>
+      </c>
+      <c r="D117" s="4" t="inlineStr">
+        <is>
+          <t>5부 10화</t>
+        </is>
+      </c>
+      <c r="E117" s="4" t="inlineStr">
+        <is>
+          <t>재정 공개와 사법 독립을 묶은 중앙위원회 결의가 표결에 오른다. 그가 스스로 넣은 자기 심사 조항도 함께다.</t>
+        </is>
+      </c>
+      <c r="F117" s="4" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="4" t="inlineStr">
+        <is>
+          <t>5부 11화</t>
+        </is>
+      </c>
+      <c r="B118" s="4" t="inlineStr">
+        <is>
+          <t>탕핑 세대</t>
+        </is>
+      </c>
+      <c r="C118" s="4" t="inlineStr">
+        <is>
+          <t>躺平的一代</t>
+        </is>
+      </c>
+      <c r="D118" s="4" t="inlineStr">
+        <is>
+          <t>5부 11화 변형</t>
+        </is>
+      </c>
+      <c r="E118" s="4" t="inlineStr">
+        <is>
+          <t>[쑤민] 청년 실업 속 배달 기사들의 임금 소송에 잉훠의 젊은 자원활동가들이 몰린다. 쑤민은 '안의 개혁'이 이 골목엔 아직 오지 않았다고 쓴다.</t>
+        </is>
+      </c>
+      <c r="F118" s="4" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="4" t="inlineStr">
+        <is>
           <t>5부 12화</t>
         </is>
       </c>
-      <c r="B116" s="4" t="inlineStr">
+      <c r="B119" s="4" t="inlineStr">
         <is>
           <t>정치국으로</t>
         </is>
       </c>
-      <c r="C116" s="4" t="inlineStr">
+      <c r="C119" s="4" t="inlineStr">
         <is>
           <t>进入政治局</t>
         </is>
       </c>
-      <c r="D116" s="4" t="inlineStr">
+      <c r="D119" s="4" t="inlineStr">
         <is>
           <t>5부 12화 변형</t>
         </is>
       </c>
-      <c r="E116" s="4" t="inlineStr">
+      <c r="E119" s="4" t="inlineStr">
         <is>
           <t>당대회 뒤 중앙위원회 전체회의에서 정치국원에 선임된다. 같은 날 민족주의 성향의 웨이창펑도 정치국에 들어온다.</t>
         </is>
       </c>
-      <c r="F116" s="4" t="inlineStr"/>
-    </row>
-    <row r="117">
-      <c r="A117" s="9" t="inlineStr">
-        <is>
-          <t>6부 1화</t>
-        </is>
-      </c>
-      <c r="B117" s="9" t="inlineStr">
-        <is>
-          <t>초대받지 않은 증인</t>
-        </is>
-      </c>
-      <c r="C117" s="9" t="inlineStr">
-        <is>
-          <t>不请自来的证人</t>
-        </is>
-      </c>
-      <c r="D117" s="9" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="E117" s="9" t="inlineStr">
-        <is>
-          <t>[쑤민] 웨이창펑 진영이 선즈위안의 '보증서' 과거를 치려고 쑤민에게 증언을 청한다. '나는 그를 비판하지만 당신들 도구는 아니에요.' 그녀는 거절한다.</t>
-        </is>
-      </c>
-      <c r="F117" s="9" t="inlineStr"/>
-    </row>
-    <row r="118">
-      <c r="A118" s="9" t="inlineStr">
-        <is>
-          <t>6부 2화</t>
-        </is>
-      </c>
-      <c r="B118" s="9" t="inlineStr">
-        <is>
-          <t>첫 정치국 회의</t>
-        </is>
-      </c>
-      <c r="C118" s="9" t="inlineStr">
-        <is>
-          <t>第一次政治局会议</t>
-        </is>
-      </c>
-      <c r="D118" s="9" t="inlineStr">
-        <is>
-          <t>6부 1·2화 변형</t>
-        </is>
-      </c>
-      <c r="E118" s="9" t="inlineStr">
-        <is>
-          <t>웨이창펑이 가격전쟁과 디플레이션을 개혁 탓으로 돌리며 공세를 편다. 그가 빠진 성 간부대회에서는 청시가 원고를 버리고 자기 말로 발언한다.</t>
-        </is>
-      </c>
-      <c r="F118" s="9" t="inlineStr"/>
-    </row>
-    <row r="119">
-      <c r="A119" s="9" t="inlineStr">
-        <is>
-          <t>6부 3화</t>
-        </is>
-      </c>
-      <c r="B119" s="9" t="inlineStr">
-        <is>
-          <t>딥페이크</t>
-        </is>
-      </c>
-      <c r="C119" s="9" t="inlineStr">
-        <is>
-          <t>深度伪造</t>
-        </is>
-      </c>
-      <c r="D119" s="9" t="inlineStr">
-        <is>
-          <t>6부 3화 변형</t>
-        </is>
-      </c>
-      <c r="E119" s="9" t="inlineStr">
-        <is>
-          <t>[쑤민] 선즈위안이 통계 조작을 지시하는 딥페이크와 함께 쑤민의 가짜 '자백 영상'도 퍼진다. 그녀는 얼굴을 드러낸 영상 한 편으로 반박한다.</t>
-        </is>
-      </c>
-      <c r="F119" s="9" t="inlineStr"/>
+      <c r="F119" s="4" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="9" t="inlineStr">
         <is>
-          <t>6부 4화</t>
+          <t>6부 1화</t>
         </is>
       </c>
       <c r="B120" s="9" t="inlineStr">
         <is>
-          <t>감사팀 흔들기</t>
+          <t>초대받지 않은 증인</t>
         </is>
       </c>
       <c r="C120" s="9" t="inlineStr">
         <is>
-          <t>动摇审计组</t>
+          <t>不请自来的证人</t>
         </is>
       </c>
       <c r="D120" s="9" t="inlineStr">
         <is>
-          <t>6부 4화 변형</t>
+          <t>신규</t>
         </is>
       </c>
       <c r="E120" s="9" t="inlineStr">
         <is>
-          <t>감사팀의 민간 감사 시절을 겨냥한 조작 스캔들이 터지고, 여름 휴양지의 원로 협의에는 그 대신 간화이구만 초대된다.</t>
+          <t>[쑤민] 웨이창펑 진영이 선즈위안의 '보증서' 과거를 치려고 쑤민에게 증언을 청한다. '나는 그를 비판하지만 당신들 도구는 아니에요.' 그녀는 거절한다.</t>
         </is>
       </c>
       <c r="F120" s="9" t="inlineStr"/>
@@ -12698,27 +12650,27 @@
     <row r="121">
       <c r="A121" s="9" t="inlineStr">
         <is>
-          <t>6부 5화</t>
+          <t>6부 2화</t>
         </is>
       </c>
       <c r="B121" s="9" t="inlineStr">
         <is>
-          <t>메이뤄란의 전언</t>
+          <t>첫 정치국 회의</t>
         </is>
       </c>
       <c r="C121" s="9" t="inlineStr">
         <is>
-          <t>梅若兰的口信</t>
+          <t>第一次政治局会议</t>
         </is>
       </c>
       <c r="D121" s="9" t="inlineStr">
         <is>
-          <t>신규</t>
+          <t>6부 1·2화 변형</t>
         </is>
       </c>
       <c r="E121" s="9" t="inlineStr">
         <is>
-          <t>[쑤민] 메이뤄란이 그의 말을 전한다. '이번 선출이 끝나면 지정거소부터 손보겠다.' 쑤민은 답한다. '약속은 받지 않아요. 조문을 보내라고 하세요.'</t>
+          <t>웨이창펑이 가격전쟁과 디플레이션을 개혁 탓으로 돌리며 공세를 편다. 그가 빠진 성 간부대회에서는 청시가 원고를 버리고 자기 말로 발언한다.</t>
         </is>
       </c>
       <c r="F121" s="9" t="inlineStr"/>
@@ -12726,27 +12678,27 @@
     <row r="122">
       <c r="A122" s="9" t="inlineStr">
         <is>
-          <t>6부 6화</t>
+          <t>6부 3화</t>
         </is>
       </c>
       <c r="B122" s="9" t="inlineStr">
         <is>
-          <t>시찰장의 폭발</t>
+          <t>딥페이크</t>
         </is>
       </c>
       <c r="C122" s="9" t="inlineStr">
         <is>
-          <t>视察现场的爆炸</t>
+          <t>深度伪造</t>
         </is>
       </c>
       <c r="D122" s="9" t="inlineStr">
         <is>
-          <t>6부 6화</t>
+          <t>6부 3화 변형</t>
         </is>
       </c>
       <c r="E122" s="9" t="inlineStr">
         <is>
-          <t>처음으로 현장을 보겠다며 따라온 우슈전. 공장 시찰장에서 폭발이 일어나 그녀가 숨지고 청시가 크게 다친다.</t>
+          <t>[쑤민] 선즈위안이 통계 조작을 지시하는 딥페이크와 함께 쑤민의 가짜 '자백 영상'도 퍼진다. 그녀는 얼굴을 드러낸 영상 한 편으로 반박한다.</t>
         </is>
       </c>
       <c r="F122" s="9" t="inlineStr"/>
@@ -12754,27 +12706,27 @@
     <row r="123">
       <c r="A123" s="9" t="inlineStr">
         <is>
-          <t>6부 7화</t>
+          <t>6부 4화</t>
         </is>
       </c>
       <c r="B123" s="9" t="inlineStr">
         <is>
-          <t>압수수색</t>
+          <t>감사팀 흔들기</t>
         </is>
       </c>
       <c r="C123" s="9" t="inlineStr">
         <is>
-          <t>搜查</t>
+          <t>动摇审计组</t>
         </is>
       </c>
       <c r="D123" s="9" t="inlineStr">
         <is>
-          <t>신규</t>
+          <t>6부 4화 변형</t>
         </is>
       </c>
       <c r="E123" s="9" t="inlineStr">
         <is>
-          <t>[쑤민] 후계 투쟁 와중의 '안정 유지' 지시로 잉훠의 창구가 수색되고 동료 둘이 강제 '여행'을 떠난다. 쑤민의 조카는 대학원 면접에서 떨어진다.</t>
+          <t>감사팀의 민간 감사 시절을 겨냥한 조작 스캔들이 터지고, 여름 휴양지의 원로 협의에는 그 대신 간화이구만 초대된다.</t>
         </is>
       </c>
       <c r="F123" s="9" t="inlineStr"/>
@@ -12782,27 +12734,27 @@
     <row r="124">
       <c r="A124" s="9" t="inlineStr">
         <is>
-          <t>6부 8화</t>
+          <t>6부 5화</t>
         </is>
       </c>
       <c r="B124" s="9" t="inlineStr">
         <is>
-          <t>배후 수사</t>
+          <t>메이뤄란의 전언</t>
         </is>
       </c>
       <c r="C124" s="9" t="inlineStr">
         <is>
-          <t>幕后调查</t>
+          <t>梅若兰的口信</t>
         </is>
       </c>
       <c r="D124" s="9" t="inlineStr">
         <is>
-          <t>6부 7·8화 변형</t>
+          <t>신규</t>
         </is>
       </c>
       <c r="E124" s="9" t="inlineStr">
         <is>
-          <t>실행범은 잡혔지만 돈은 유령회사 뒤로 사라진다. 웨이창펑 진영의 참모가 옛 성위서기 인맥과 이어져 있음이 드러난다.</t>
+          <t>[쑤민] 메이뤄란이 그의 말을 전한다. '이번 선출이 끝나면 지정거소부터 손보겠다.' 쑤민은 답한다. '약속은 받지 않아요. 조문을 보내라고 하세요.'</t>
         </is>
       </c>
       <c r="F124" s="9" t="inlineStr"/>
@@ -12810,27 +12762,27 @@
     <row r="125">
       <c r="A125" s="9" t="inlineStr">
         <is>
-          <t>6부 9화</t>
+          <t>6부 6화</t>
         </is>
       </c>
       <c r="B125" s="9" t="inlineStr">
         <is>
-          <t>엇갈림</t>
+          <t>시찰장의 폭발</t>
         </is>
       </c>
       <c r="C125" s="9" t="inlineStr">
         <is>
-          <t>擦肩而过</t>
+          <t>视察现场的爆炸</t>
         </is>
       </c>
       <c r="D125" s="9" t="inlineStr">
         <is>
-          <t>6부 5화 변형</t>
+          <t>6부 6화</t>
         </is>
       </c>
       <c r="E125" s="9" t="inlineStr">
         <is>
-          <t>[쑤민] 탕쉐의 옛 마을 사람들이 쑤민에게 차를 낸다. 그녀는 바로 전날 선즈위안이 같은 자리에 앉아 같은 차를 마셨다는 것을 알게 된다.</t>
+          <t>처음으로 현장을 보겠다며 따라온 우슈전. 공장 시찰장에서 폭발이 일어나 그녀가 숨지고 청시가 크게 다친다.</t>
         </is>
       </c>
       <c r="F125" s="9" t="inlineStr"/>
@@ -12838,27 +12790,27 @@
     <row r="126">
       <c r="A126" s="9" t="inlineStr">
         <is>
-          <t>6부 10화</t>
+          <t>6부 7화</t>
         </is>
       </c>
       <c r="B126" s="9" t="inlineStr">
         <is>
-          <t>정치국의 격돌</t>
+          <t>압수수색</t>
         </is>
       </c>
       <c r="C126" s="9" t="inlineStr">
         <is>
-          <t>政治局的交锋</t>
+          <t>搜查</t>
         </is>
       </c>
       <c r="D126" s="9" t="inlineStr">
         <is>
-          <t>6부 9화 변형</t>
+          <t>신규</t>
         </is>
       </c>
       <c r="E126" s="9" t="inlineStr">
         <is>
-          <t>비공개 확대회의에서 두 후보가 정면으로 토론한다. 청시는 병실에서 녹취를 들으며 메모를 보낸다.</t>
+          <t>[쑤민] 후계 투쟁 와중의 '안정 유지' 지시로 잉훠의 창구가 수색되고 동료 둘이 강제 '여행'을 떠난다. 쑤민의 조카는 대학원 면접에서 떨어진다.</t>
         </is>
       </c>
       <c r="F126" s="9" t="inlineStr"/>
@@ -12866,27 +12818,27 @@
     <row r="127">
       <c r="A127" s="9" t="inlineStr">
         <is>
-          <t>6부 11화</t>
+          <t>6부 8화</t>
         </is>
       </c>
       <c r="B127" s="9" t="inlineStr">
         <is>
-          <t>반송된 편지</t>
+          <t>배후 수사</t>
         </is>
       </c>
       <c r="C127" s="9" t="inlineStr">
         <is>
-          <t>退回的信</t>
+          <t>幕后调查</t>
         </is>
       </c>
       <c r="D127" s="9" t="inlineStr">
         <is>
-          <t>신규</t>
+          <t>6부 7·8화 변형</t>
         </is>
       </c>
       <c r="E127" s="9" t="inlineStr">
         <is>
-          <t>[쑤민] 쑤민은 '누가 이기든 지정거소를 없애라'는 손편지를 중앙위원 전원에게 보낸다. 거의 모두 반송되고, 한 통만 돌아오지 않는다.</t>
+          <t>실행범은 잡혔지만 돈은 유령회사 뒤로 사라진다. 웨이창펑 진영의 참모가 옛 성위서기 인맥과 이어져 있음이 드러난다.</t>
         </is>
       </c>
       <c r="F127" s="9" t="inlineStr"/>
@@ -12894,139 +12846,139 @@
     <row r="128">
       <c r="A128" s="9" t="inlineStr">
         <is>
+          <t>6부 9화</t>
+        </is>
+      </c>
+      <c r="B128" s="9" t="inlineStr">
+        <is>
+          <t>엇갈림</t>
+        </is>
+      </c>
+      <c r="C128" s="9" t="inlineStr">
+        <is>
+          <t>擦肩而过</t>
+        </is>
+      </c>
+      <c r="D128" s="9" t="inlineStr">
+        <is>
+          <t>6부 5화 변형</t>
+        </is>
+      </c>
+      <c r="E128" s="9" t="inlineStr">
+        <is>
+          <t>[쑤민] 탕쉐의 옛 마을 사람들이 쑤민에게 차를 낸다. 그녀는 바로 전날 선즈위안이 같은 자리에 앉아 같은 차를 마셨다는 것을 알게 된다.</t>
+        </is>
+      </c>
+      <c r="F128" s="9" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="9" t="inlineStr">
+        <is>
+          <t>6부 10화</t>
+        </is>
+      </c>
+      <c r="B129" s="9" t="inlineStr">
+        <is>
+          <t>정치국의 격돌</t>
+        </is>
+      </c>
+      <c r="C129" s="9" t="inlineStr">
+        <is>
+          <t>政治局的交锋</t>
+        </is>
+      </c>
+      <c r="D129" s="9" t="inlineStr">
+        <is>
+          <t>6부 9화 변형</t>
+        </is>
+      </c>
+      <c r="E129" s="9" t="inlineStr">
+        <is>
+          <t>비공개 확대회의에서 두 후보가 정면으로 토론한다. 청시는 병실에서 녹취를 들으며 메모를 보낸다.</t>
+        </is>
+      </c>
+      <c r="F129" s="9" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="9" t="inlineStr">
+        <is>
+          <t>6부 11화</t>
+        </is>
+      </c>
+      <c r="B130" s="9" t="inlineStr">
+        <is>
+          <t>반송된 편지</t>
+        </is>
+      </c>
+      <c r="C130" s="9" t="inlineStr">
+        <is>
+          <t>退回的信</t>
+        </is>
+      </c>
+      <c r="D130" s="9" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="E130" s="9" t="inlineStr">
+        <is>
+          <t>[쑤민] 쑤민은 '누가 이기든 지정거소를 없애라'는 손편지를 중앙위원 전원에게 보낸다. 거의 모두 반송되고, 한 통만 돌아오지 않는다.</t>
+        </is>
+      </c>
+      <c r="F130" s="9" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="9" t="inlineStr">
+        <is>
           <t>6부 12화</t>
         </is>
       </c>
-      <c r="B128" s="9" t="inlineStr">
+      <c r="B131" s="9" t="inlineStr">
         <is>
           <t>총서기 선출</t>
         </is>
       </c>
-      <c r="C128" s="9" t="inlineStr">
+      <c r="C131" s="9" t="inlineStr">
         <is>
           <t>当选总书记</t>
         </is>
       </c>
-      <c r="D128" s="9" t="inlineStr">
+      <c r="D131" s="9" t="inlineStr">
         <is>
           <t>6부 10·11·12화 변형</t>
         </is>
       </c>
-      <c r="E128" s="9" t="inlineStr">
+      <c r="E131" s="9" t="inlineStr">
         <is>
           <t>붕대를 감은 청시가 중앙위원들을 설득한 끝에, 첫 실질 경쟁 표결에서 근소한 차로 총서기에 선출된다. 웨이창펑이 승복한다. 그 책상엔 반송되지 않은 편지 한 통.</t>
         </is>
       </c>
-      <c r="F128" s="9" t="inlineStr"/>
-    </row>
-    <row r="129">
-      <c r="A129" s="4" t="inlineStr">
-        <is>
-          <t>7부 1화</t>
-        </is>
-      </c>
-      <c r="B129" s="4" t="inlineStr">
-        <is>
-          <t>첫해</t>
-        </is>
-      </c>
-      <c r="C129" s="4" t="inlineStr">
-        <is>
-          <t>第一年</t>
-        </is>
-      </c>
-      <c r="D129" s="4" t="inlineStr">
-        <is>
-          <t>7부 1화</t>
-        </is>
-      </c>
-      <c r="E129" s="4" t="inlineStr">
-        <is>
-          <t>총서기 취임 한 달. 우슈전의 빈 책상이 남아 있고 청시는 팔 재활을 하며 판공청 주임 일을 시작한다.</t>
-        </is>
-      </c>
-      <c r="F129" s="4" t="inlineStr"/>
-    </row>
-    <row r="130">
-      <c r="A130" s="4" t="inlineStr">
-        <is>
-          <t>7부 2화</t>
-        </is>
-      </c>
-      <c r="B130" s="4" t="inlineStr">
-        <is>
-          <t>복합위기</t>
-        </is>
-      </c>
-      <c r="C130" s="4" t="inlineStr">
-        <is>
-          <t>复合危机</t>
-        </is>
-      </c>
-      <c r="D130" s="4" t="inlineStr">
-        <is>
-          <t>7부 2화</t>
-        </is>
-      </c>
-      <c r="E130" s="4" t="inlineStr">
-        <is>
-          <t>기록적 극한 호우와 지방채 연쇄부도, 국경 긴장이 한꺼번에 터진다. 국가안전위원회가 밤새 소집된다.</t>
-        </is>
-      </c>
-      <c r="F130" s="4" t="inlineStr"/>
-    </row>
-    <row r="131">
-      <c r="A131" s="4" t="inlineStr">
-        <is>
-          <t>7부 3화</t>
-        </is>
-      </c>
-      <c r="B131" s="4" t="inlineStr">
-        <is>
-          <t>전권의 유혹</t>
-        </is>
-      </c>
-      <c r="C131" s="4" t="inlineStr">
-        <is>
-          <t>全权的诱惑</t>
-        </is>
-      </c>
-      <c r="D131" s="4" t="inlineStr">
-        <is>
-          <t>7부 3화</t>
-        </is>
-      </c>
-      <c r="E131" s="4" t="inlineStr">
-        <is>
-          <t>사오톄쥔이 군 지휘부까지 겨눌 '청원 행동' 반부패 영도소조에 초법적 권한을 주자고 내민다. 부패를 끝낼 칼이라는 논리다.</t>
-        </is>
-      </c>
-      <c r="F131" s="4" t="inlineStr"/>
+      <c r="F131" s="9" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="4" t="inlineStr">
         <is>
-          <t>7부 4화</t>
+          <t>7부 1화</t>
         </is>
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>임기 제한 폐지론</t>
+          <t>첫해</t>
         </is>
       </c>
       <c r="C132" s="4" t="inlineStr">
         <is>
-          <t>废除任期限制论</t>
+          <t>第一年</t>
         </is>
       </c>
       <c r="D132" s="4" t="inlineStr">
         <is>
-          <t>7부 4화</t>
+          <t>7부 1화</t>
         </is>
       </c>
       <c r="E132" s="4" t="inlineStr">
         <is>
-          <t>위기 속에서 '임기 제한 폐지' 개헌 초안이 처음으로 공식 테이블에 오른다. 박수 소리가 너무 빨리 나온다.</t>
+          <t>총서기 취임 한 달. 우슈전의 빈 책상이 남아 있고 청시는 팔 재활을 하며 판공청 주임 일을 시작한다.</t>
         </is>
       </c>
       <c r="F132" s="4" t="inlineStr"/>
@@ -13034,27 +12986,27 @@
     <row r="133">
       <c r="A133" s="4" t="inlineStr">
         <is>
-          <t>7부 5화</t>
+          <t>7부 2화</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>제한적 통제</t>
+          <t>복합위기</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>有限管控</t>
+          <t>复合危机</t>
         </is>
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>7부 5화 변형</t>
+          <t>7부 2화</t>
         </is>
       </c>
       <c r="E133" s="4" t="inlineStr">
         <is>
-          <t>국경 위협을 부풀린 허위정보가 퍼지자 인터넷 통제안이 올라온다. 그는 '한시적·제한적'이라는 단서를 달아 결재한다.</t>
+          <t>기록적 극한 호우와 지방채 연쇄부도, 국경 긴장이 한꺼번에 터진다. 국가안전위원회가 밤새 소집된다.</t>
         </is>
       </c>
       <c r="F133" s="4" t="inlineStr"/>
@@ -13062,27 +13014,27 @@
     <row r="134">
       <c r="A134" s="4" t="inlineStr">
         <is>
-          <t>7부 6화</t>
+          <t>7부 3화</t>
         </is>
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>감사팀에게 한 부탁</t>
+          <t>전권의 유혹</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
-          <t>对审计组的请求</t>
+          <t>全权的诱惑</t>
         </is>
       </c>
       <c r="D134" s="4" t="inlineStr">
         <is>
-          <t>7부 6화</t>
+          <t>7부 3화</t>
         </is>
       </c>
       <c r="E134" s="4" t="inlineStr">
         <is>
-          <t>국방 조달 감사에서 불편한 사실이 나온다. 그는 정치밍에게 발표를 잠시 미뤄 달라고 부탁한다.</t>
+          <t>사오톄쥔이 군 지휘부까지 겨눌 '청원 행동' 반부패 영도소조에 초법적 권한을 주자고 내민다. 부패를 끝낼 칼이라는 논리다.</t>
         </is>
       </c>
       <c r="F134" s="4" t="inlineStr"/>
@@ -13090,27 +13042,27 @@
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
         <is>
-          <t>7부 7화</t>
+          <t>7부 4화</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>작은 월권</t>
+          <t>임기 제한 폐지론</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>小小的越权</t>
+          <t>废除任期限制论</t>
         </is>
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>7부 7화</t>
+          <t>7부 4화</t>
         </is>
       </c>
       <c r="E135" s="4" t="inlineStr">
         <is>
-          <t>국경 돌발 상황의 밤, 그는 상무위원회 절차 없이 직접 명령을 내린다. 결과는 옳았지만 절차는 무너졌다.</t>
+          <t>위기 속에서 '임기 제한 폐지' 개헌 초안이 처음으로 공식 테이블에 오른다. 박수 소리가 너무 빨리 나온다.</t>
         </is>
       </c>
       <c r="F135" s="4" t="inlineStr"/>
@@ -13118,27 +13070,27 @@
     <row r="136">
       <c r="A136" s="4" t="inlineStr">
         <is>
-          <t>7부 8화</t>
+          <t>7부 5화</t>
         </is>
       </c>
       <c r="B136" s="4" t="inlineStr">
         <is>
-          <t>다시, 차 마시자</t>
+          <t>제한적 통제</t>
         </is>
       </c>
       <c r="C136" s="4" t="inlineStr">
         <is>
-          <t>再喝一次茶</t>
+          <t>有限管控</t>
         </is>
       </c>
       <c r="D136" s="4" t="inlineStr">
         <is>
-          <t>신규</t>
+          <t>7부 5화 변형</t>
         </is>
       </c>
       <c r="E136" s="4" t="inlineStr">
         <is>
-          <t>[쑤민] '청원 행동'의 해외 연계 명단에 잉훠가 오르고, 쑤민이 지정거소감시거주로 끌려간다. 공문 맨 위에는 총서기의 결재 번호가 찍혀 있다.</t>
+          <t>국경 위협을 부풀린 허위정보가 퍼지자 인터넷 통제안이 올라온다. 그는 '한시적·제한적'이라는 단서를 달아 결재한다.</t>
         </is>
       </c>
       <c r="F136" s="4" t="inlineStr"/>
@@ -13146,27 +13098,27 @@
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
         <is>
-          <t>7부 9화</t>
+          <t>7부 6화</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>청시의 정면 대결</t>
+          <t>감사팀에게 한 부탁</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>程曦的正面交锋</t>
+          <t>对审计组的请求</t>
         </is>
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>7부 8화 변형</t>
+          <t>7부 6화</t>
         </is>
       </c>
       <c r="E137" s="4" t="inlineStr">
         <is>
-          <t>사오톄쥔이 비상체계를 상설화하는 수정안을 들고 오자, 청시가 처음으로 총서기에게 공개적으로 반대하며 잉훠 명단을 탁자에 올린다.</t>
+          <t>국방 조달 감사에서 불편한 사실이 나온다. 그는 정치밍에게 발표를 잠시 미뤄 달라고 부탁한다.</t>
         </is>
       </c>
       <c r="F137" s="4" t="inlineStr"/>
@@ -13174,27 +13126,27 @@
     <row r="138">
       <c r="A138" s="4" t="inlineStr">
         <is>
-          <t>7부 10화</t>
+          <t>7부 7화</t>
         </is>
       </c>
       <c r="B138" s="4" t="inlineStr">
         <is>
-          <t>세 번째 만남</t>
+          <t>작은 월권</t>
         </is>
       </c>
       <c r="C138" s="4" t="inlineStr">
         <is>
-          <t>第三次见面</t>
+          <t>小小的越权</t>
         </is>
       </c>
       <c r="D138" s="4" t="inlineStr">
         <is>
-          <t>7부 9화 변형</t>
+          <t>7부 7화</t>
         </is>
       </c>
       <c r="E138" s="4" t="inlineStr">
         <is>
-          <t>메이뤄란이 한서우이의 기록과 쑤민의 행방을 함께 건넨다. 지정거소 시설의 방에서 그녀가 묻는다. '차 마실래? 여긴 너희가 차 마시자고 부르는 곳이잖아.'</t>
+          <t>국경 돌발 상황의 밤, 그는 상무위원회 절차 없이 직접 명령을 내린다. 결과는 옳았지만 절차는 무너졌다.</t>
         </is>
       </c>
       <c r="F138" s="4" t="inlineStr"/>
@@ -13202,27 +13154,27 @@
     <row r="139">
       <c r="A139" s="4" t="inlineStr">
         <is>
-          <t>7부 11화</t>
+          <t>7부 8화</t>
         </is>
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>벼랑 끝에서 놓다</t>
+          <t>다시, 차 마시자</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>悬崖边放手</t>
+          <t>再喝一次茶</t>
         </is>
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>7부 10화</t>
+          <t>신규</t>
         </is>
       </c>
       <c r="E139" s="4" t="inlineStr">
         <is>
-          <t>가장 심각한 국경 위기가 터진 밤, 사오톄쥔이 전권 위임서를 내민다. 그는 서명하지 않고 상무위원회를 소집한다.</t>
+          <t>[쑤민] '청원 행동'의 해외 연계 명단에 잉훠가 오르고, 쑤민이 지정거소감시거주로 끌려간다. 공문 맨 위에는 총서기의 결재 번호가 찍혀 있다.</t>
         </is>
       </c>
       <c r="F139" s="4" t="inlineStr"/>
@@ -13230,129 +13182,129 @@
     <row r="140">
       <c r="A140" s="4" t="inlineStr">
         <is>
+          <t>7부 9화</t>
+        </is>
+      </c>
+      <c r="B140" s="4" t="inlineStr">
+        <is>
+          <t>청시의 정면 대결</t>
+        </is>
+      </c>
+      <c r="C140" s="4" t="inlineStr">
+        <is>
+          <t>程曦的正面交锋</t>
+        </is>
+      </c>
+      <c r="D140" s="4" t="inlineStr">
+        <is>
+          <t>7부 8화 변형</t>
+        </is>
+      </c>
+      <c r="E140" s="4" t="inlineStr">
+        <is>
+          <t>사오톄쥔이 비상체계를 상설화하는 수정안을 들고 오자, 청시가 처음으로 총서기에게 공개적으로 반대하며 잉훠 명단을 탁자에 올린다.</t>
+        </is>
+      </c>
+      <c r="F140" s="4" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="4" t="inlineStr">
+        <is>
+          <t>7부 10화</t>
+        </is>
+      </c>
+      <c r="B141" s="4" t="inlineStr">
+        <is>
+          <t>세 번째 만남</t>
+        </is>
+      </c>
+      <c r="C141" s="4" t="inlineStr">
+        <is>
+          <t>第三次见面</t>
+        </is>
+      </c>
+      <c r="D141" s="4" t="inlineStr">
+        <is>
+          <t>7부 9화 변형</t>
+        </is>
+      </c>
+      <c r="E141" s="4" t="inlineStr">
+        <is>
+          <t>메이뤄란이 한서우이의 기록과 쑤민의 행방을 함께 건넨다. 지정거소 시설의 방에서 그녀가 묻는다. '차 마실래? 여긴 너희가 차 마시자고 부르는 곳이잖아.'</t>
+        </is>
+      </c>
+      <c r="F141" s="4" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="4" t="inlineStr">
+        <is>
+          <t>7부 11화</t>
+        </is>
+      </c>
+      <c r="B142" s="4" t="inlineStr">
+        <is>
+          <t>벼랑 끝에서 놓다</t>
+        </is>
+      </c>
+      <c r="C142" s="4" t="inlineStr">
+        <is>
+          <t>悬崖边放手</t>
+        </is>
+      </c>
+      <c r="D142" s="4" t="inlineStr">
+        <is>
+          <t>7부 10화</t>
+        </is>
+      </c>
+      <c r="E142" s="4" t="inlineStr">
+        <is>
+          <t>가장 심각한 국경 위기가 터진 밤, 사오톄쥔이 전권 위임서를 내민다. 그는 서명하지 않고 상무위원회를 소집한다.</t>
+        </is>
+      </c>
+      <c r="F142" s="4" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="4" t="inlineStr">
+        <is>
           <t>7부 12화</t>
         </is>
       </c>
-      <c r="B140" s="4" t="inlineStr">
+      <c r="B143" s="4" t="inlineStr">
         <is>
           <t>새로운 균형</t>
         </is>
       </c>
-      <c r="C140" s="4" t="inlineStr">
+      <c r="C143" s="4" t="inlineStr">
         <is>
           <t>新的平衡</t>
         </is>
       </c>
-      <c r="D140" s="4" t="inlineStr">
+      <c r="D143" s="4" t="inlineStr">
         <is>
           <t>7부 11·12화 변형</t>
         </is>
       </c>
-      <c r="E140" s="4" t="inlineStr">
+      <c r="E143" s="4" t="inlineStr">
         <is>
           <t>임기 제한 폐지안을 철회하고 위기 결정은 상무위 다수결로 한다고 발표한다. 쑤민은 조용히 풀려나지만 사과문은 없다. 간화이구가 '이제야 네가 돌아왔다'고 말한다.</t>
         </is>
       </c>
-      <c r="F140" s="4" t="inlineStr"/>
-    </row>
-    <row r="141">
-      <c r="A141" s="9" t="inlineStr">
-        <is>
-          <t>8부 1화</t>
-        </is>
-      </c>
-      <c r="B141" s="9" t="inlineStr">
-        <is>
-          <t>풀려난 날</t>
-        </is>
-      </c>
-      <c r="C141" s="9" t="inlineStr">
-        <is>
-          <t>获释那天</t>
-        </is>
-      </c>
-      <c r="D141" s="9" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="E141" s="9" t="inlineStr">
-        <is>
-          <t>[쑤민] 지정거소에서 나온 날, 집 앞 감시 카메라는 그대로다. 쑤민은 처음으로 '제자리 망명'이라는 말을 쓰고, 어머니는 더는 묻지 않는다.</t>
-        </is>
-      </c>
-      <c r="F141" s="9" t="inlineStr"/>
-    </row>
-    <row r="142">
-      <c r="A142" s="9" t="inlineStr">
-        <is>
-          <t>8부 2화</t>
-        </is>
-      </c>
-      <c r="B142" s="9" t="inlineStr">
-        <is>
-          <t>권력의 경계</t>
-        </is>
-      </c>
-      <c r="C142" s="9" t="inlineStr">
-        <is>
-          <t>权力的边界</t>
-        </is>
-      </c>
-      <c r="D142" s="9" t="inlineStr">
-        <is>
-          <t>8부 1화</t>
-        </is>
-      </c>
-      <c r="E142" s="9" t="inlineStr">
-        <is>
-          <t>총서기 권한을 스스로 줄이는 '권력의 경계' 패키지에 착수한다. 임기 2기 제한 복원이 첫 줄에 적힌다.</t>
-        </is>
-      </c>
-      <c r="F142" s="9" t="inlineStr"/>
-    </row>
-    <row r="143">
-      <c r="A143" s="9" t="inlineStr">
-        <is>
-          <t>8부 3화</t>
-        </is>
-      </c>
-      <c r="B143" s="9" t="inlineStr">
-        <is>
-          <t>빨간 펜</t>
-        </is>
-      </c>
-      <c r="C143" s="9" t="inlineStr">
-        <is>
-          <t>红笔</t>
-        </is>
-      </c>
-      <c r="D143" s="9" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="E143" s="9" t="inlineStr">
-        <is>
-          <t>[쑤민] 메이뤄란이 들고 온 '지정거소감시거주 제한' 초안을 쑤민이 빨간 펜으로 고쳐 돌려보낸다. 수정안은 '익명 법률가 의견'으로 그대로 반영된다.</t>
-        </is>
-      </c>
-      <c r="F143" s="9" t="inlineStr"/>
+      <c r="F143" s="4" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="9" t="inlineStr">
         <is>
-          <t>8부 4화</t>
+          <t>8부 1화</t>
         </is>
       </c>
       <c r="B144" s="9" t="inlineStr">
         <is>
-          <t>해임 조항</t>
+          <t>풀려난 날</t>
         </is>
       </c>
       <c r="C144" s="9" t="inlineStr">
         <is>
-          <t>罢免条款</t>
+          <t>获释那天</t>
         </is>
       </c>
       <c r="D144" s="9" t="inlineStr">
@@ -13362,7 +13314,7 @@
       </c>
       <c r="E144" s="9" t="inlineStr">
         <is>
-          <t>그는 직접 '총서기 해임 절차'를 써 넣는다. 정치국원 3분의 1 발의, 확대회의, 중앙위원회 과반. 청시가 묻는다. '당신 자신에게 겨눈 총인가요?'</t>
+          <t>[쑤민] 지정거소에서 나온 날, 집 앞 감시 카메라는 그대로다. 쑤민은 처음으로 '제자리 망명'이라는 말을 쓰고, 어머니는 더는 묻지 않는다.</t>
         </is>
       </c>
       <c r="F144" s="9" t="inlineStr"/>
@@ -13370,27 +13322,27 @@
     <row r="145">
       <c r="A145" s="9" t="inlineStr">
         <is>
-          <t>8부 5화</t>
+          <t>8부 2화</t>
         </is>
       </c>
       <c r="B145" s="9" t="inlineStr">
         <is>
-          <t>돌아온 병사들</t>
+          <t>권력의 경계</t>
         </is>
       </c>
       <c r="C145" s="9" t="inlineStr">
         <is>
-          <t>归来的士兵</t>
+          <t>权力的边界</t>
         </is>
       </c>
       <c r="D145" s="9" t="inlineStr">
         <is>
-          <t>8부 3화 변형</t>
+          <t>8부 1화</t>
         </is>
       </c>
       <c r="E145" s="9" t="inlineStr">
         <is>
-          <t>[쑤민] 국경 휴전 뒤 돌아온 퇴역군인들이 일자리와 연금 청원을 들고 잉훠 창구에 줄을 선다. 쑤민은 군복 입은 의뢰인을 처음 받는다.</t>
+          <t>총서기 권한을 스스로 줄이는 '권력의 경계' 패키지에 착수한다. 임기 2기 제한 복원이 첫 줄에 적힌다.</t>
         </is>
       </c>
       <c r="F145" s="9" t="inlineStr"/>
@@ -13398,27 +13350,27 @@
     <row r="146">
       <c r="A146" s="9" t="inlineStr">
         <is>
-          <t>8부 6화</t>
+          <t>8부 3화</t>
         </is>
       </c>
       <c r="B146" s="9" t="inlineStr">
         <is>
-          <t>커팅웨와의 마지막 대화</t>
+          <t>빨간 펜</t>
         </is>
       </c>
       <c r="C146" s="9" t="inlineStr">
         <is>
-          <t>与柯庭岳的最后对话</t>
+          <t>红笔</t>
         </is>
       </c>
       <c r="D146" s="9" t="inlineStr">
         <is>
-          <t>8부 5화</t>
+          <t>신규</t>
         </is>
       </c>
       <c r="E146" s="9" t="inlineStr">
         <is>
-          <t>병색이 짙은 커팅웨를 찾아간다. 격자화 관리와 안면인식의 유산을 걷어낼 법안과 예란의 밤을 묻는다.</t>
+          <t>[쑤민] 메이뤄란이 들고 온 '지정거소감시거주 제한' 초안을 쑤민이 빨간 펜으로 고쳐 돌려보낸다. 수정안은 '익명 법률가 의견'으로 그대로 반영된다.</t>
         </is>
       </c>
       <c r="F146" s="9" t="inlineStr"/>
@@ -13426,27 +13378,27 @@
     <row r="147">
       <c r="A147" s="9" t="inlineStr">
         <is>
-          <t>8부 7화</t>
+          <t>8부 4화</t>
         </is>
       </c>
       <c r="B147" s="9" t="inlineStr">
         <is>
-          <t>세대의 청원</t>
+          <t>해임 조항</t>
         </is>
       </c>
       <c r="C147" s="9" t="inlineStr">
         <is>
-          <t>一代人的请愿</t>
+          <t>罢免条款</t>
         </is>
       </c>
       <c r="D147" s="9" t="inlineStr">
         <is>
-          <t>8부 4화 변형</t>
+          <t>신규</t>
         </is>
       </c>
       <c r="E147" s="9" t="inlineStr">
         <is>
-          <t>[쑤민] 정년 연장·연금 불공평에 분노한 노동자 청원을 쑤민이 대리한다. 그녀는 실명 기고로 '권력의 경계'가 노동자의 경계는 넓히지 않았다고 그의 정부를 비판한다.</t>
+          <t>그는 직접 '총서기 해임 절차'를 써 넣는다. 정치국원 3분의 1 발의, 확대회의, 중앙위원회 과반. 청시가 묻는다. '당신 자신에게 겨눈 총인가요?'</t>
         </is>
       </c>
       <c r="F147" s="9" t="inlineStr"/>
@@ -13454,27 +13406,27 @@
     <row r="148">
       <c r="A148" s="9" t="inlineStr">
         <is>
-          <t>8부 8화</t>
+          <t>8부 5화</t>
         </is>
       </c>
       <c r="B148" s="9" t="inlineStr">
         <is>
-          <t>마지막 결전</t>
+          <t>돌아온 병사들</t>
         </is>
       </c>
       <c r="C148" s="9" t="inlineStr">
         <is>
-          <t>最后的决战</t>
+          <t>归来的士兵</t>
         </is>
       </c>
       <c r="D148" s="9" t="inlineStr">
         <is>
-          <t>8부 8화</t>
+          <t>8부 3화 변형</t>
         </is>
       </c>
       <c r="E148" s="9" t="inlineStr">
         <is>
-          <t>원로·정법계가 기율위·관영매체·전체회의 네 전선에서 총공세를 편다. 그 한가운데서 정치밍이 쓰러진다.</t>
+          <t>[쑤민] 국경 휴전 뒤 돌아온 퇴역군인들이 일자리와 연금 청원을 들고 잉훠 창구에 줄을 선다. 쑤민은 군복 입은 의뢰인을 처음 받는다.</t>
         </is>
       </c>
       <c r="F148" s="9" t="inlineStr"/>
@@ -13482,27 +13434,27 @@
     <row r="149">
       <c r="A149" s="9" t="inlineStr">
         <is>
-          <t>8부 9화</t>
+          <t>8부 6화</t>
         </is>
       </c>
       <c r="B149" s="9" t="inlineStr">
         <is>
-          <t>서수이성의 빚</t>
+          <t>커팅웨와의 마지막 대화</t>
         </is>
       </c>
       <c r="C149" s="9" t="inlineStr">
         <is>
-          <t>西水省的债</t>
+          <t>与柯庭岳的最后对话</t>
         </is>
       </c>
       <c r="D149" s="9" t="inlineStr">
         <is>
-          <t>8부 7화 변형</t>
+          <t>8부 5화</t>
         </is>
       </c>
       <c r="E149" s="9" t="inlineStr">
         <is>
-          <t>[쑤민] 희토류 값 폭락으로 서수이성 교사 월급이 끊긴다. 임금 소송을 돕던 쑤민이 숨은 채무를 공개한 성위서기 녜추와 처음 마주 앉는다.</t>
+          <t>병색이 짙은 커팅웨를 찾아간다. 격자화 관리와 안면인식의 유산을 걷어낼 법안과 예란의 밤을 묻는다.</t>
         </is>
       </c>
       <c r="F149" s="9" t="inlineStr"/>
@@ -13510,27 +13462,27 @@
     <row r="150">
       <c r="A150" s="9" t="inlineStr">
         <is>
-          <t>8부 10화</t>
+          <t>8부 7화</t>
         </is>
       </c>
       <c r="B150" s="9" t="inlineStr">
         <is>
-          <t>전체회의 확정</t>
+          <t>세대의 청원</t>
         </is>
       </c>
       <c r="C150" s="9" t="inlineStr">
         <is>
-          <t>全会通过</t>
+          <t>一代人的请愿</t>
         </is>
       </c>
       <c r="D150" s="9" t="inlineStr">
         <is>
-          <t>8부 9화 변형</t>
+          <t>8부 4화 변형</t>
         </is>
       </c>
       <c r="E150" s="9" t="inlineStr">
         <is>
-          <t>정치밍의 장례 일주일 뒤, 2기 제한·집체영도·지정거소 제한·해임 절차가 당장과 헌법 개정안에 확정된다. 해임 조항에는 반대표가 가장 적다.</t>
+          <t>[쑤민] 정년 연장·연금 불공평에 분노한 노동자 청원을 쑤민이 대리한다. 그녀는 실명 기고로 '권력의 경계'가 노동자의 경계는 넓히지 않았다고 그의 정부를 비판한다.</t>
         </is>
       </c>
       <c r="F150" s="9" t="inlineStr"/>
@@ -13538,27 +13490,27 @@
     <row r="151">
       <c r="A151" s="9" t="inlineStr">
         <is>
-          <t>8부 11화</t>
+          <t>8부 8화</t>
         </is>
       </c>
       <c r="B151" s="9" t="inlineStr">
         <is>
-          <t>용서가 아니라</t>
+          <t>마지막 결전</t>
         </is>
       </c>
       <c r="C151" s="9" t="inlineStr">
         <is>
-          <t>不是宽恕</t>
+          <t>最后的决战</t>
         </is>
       </c>
       <c r="D151" s="9" t="inlineStr">
         <is>
-          <t>8부 11화 변형</t>
+          <t>8부 8화</t>
         </is>
       </c>
       <c r="E151" s="9" t="inlineStr">
         <is>
-          <t>[쑤민] 뤄전방 판결의 날, '해외 세력' 낙인 조례 폐지 논의가 시작된다. 쑤민은 사면 신청 양식을 찢고 '용서가 아니라 복권'을 요구하는 청원을 낸다.</t>
+          <t>원로·정법계가 기율위·관영매체·전체회의 네 전선에서 총공세를 편다. 그 한가운데서 정치밍이 쓰러진다.</t>
         </is>
       </c>
       <c r="F151" s="9" t="inlineStr"/>
@@ -13566,139 +13518,139 @@
     <row r="152">
       <c r="A152" s="9" t="inlineStr">
         <is>
+          <t>8부 9화</t>
+        </is>
+      </c>
+      <c r="B152" s="9" t="inlineStr">
+        <is>
+          <t>서수이성의 빚</t>
+        </is>
+      </c>
+      <c r="C152" s="9" t="inlineStr">
+        <is>
+          <t>西水省的债</t>
+        </is>
+      </c>
+      <c r="D152" s="9" t="inlineStr">
+        <is>
+          <t>8부 7화 변형</t>
+        </is>
+      </c>
+      <c r="E152" s="9" t="inlineStr">
+        <is>
+          <t>[쑤민] 희토류 값 폭락으로 서수이성 교사 월급이 끊긴다. 임금 소송을 돕던 쑤민이 숨은 채무를 공개한 성위서기 녜추와 처음 마주 앉는다.</t>
+        </is>
+      </c>
+      <c r="F152" s="9" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="9" t="inlineStr">
+        <is>
+          <t>8부 10화</t>
+        </is>
+      </c>
+      <c r="B153" s="9" t="inlineStr">
+        <is>
+          <t>전체회의 확정</t>
+        </is>
+      </c>
+      <c r="C153" s="9" t="inlineStr">
+        <is>
+          <t>全会通过</t>
+        </is>
+      </c>
+      <c r="D153" s="9" t="inlineStr">
+        <is>
+          <t>8부 9화 변형</t>
+        </is>
+      </c>
+      <c r="E153" s="9" t="inlineStr">
+        <is>
+          <t>정치밍의 장례 일주일 뒤, 2기 제한·집체영도·지정거소 제한·해임 절차가 당장과 헌법 개정안에 확정된다. 해임 조항에는 반대표가 가장 적다.</t>
+        </is>
+      </c>
+      <c r="F153" s="9" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="9" t="inlineStr">
+        <is>
+          <t>8부 11화</t>
+        </is>
+      </c>
+      <c r="B154" s="9" t="inlineStr">
+        <is>
+          <t>용서가 아니라</t>
+        </is>
+      </c>
+      <c r="C154" s="9" t="inlineStr">
+        <is>
+          <t>不是宽恕</t>
+        </is>
+      </c>
+      <c r="D154" s="9" t="inlineStr">
+        <is>
+          <t>8부 11화 변형</t>
+        </is>
+      </c>
+      <c r="E154" s="9" t="inlineStr">
+        <is>
+          <t>[쑤민] 뤄전방 판결의 날, '해외 세력' 낙인 조례 폐지 논의가 시작된다. 쑤민은 사면 신청 양식을 찢고 '용서가 아니라 복권'을 요구하는 청원을 낸다.</t>
+        </is>
+      </c>
+      <c r="F154" s="9" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="9" t="inlineStr">
+        <is>
           <t>8부 12화</t>
         </is>
       </c>
-      <c r="B152" s="9" t="inlineStr">
+      <c r="B155" s="9" t="inlineStr">
         <is>
           <t>차를 잊지 마</t>
         </is>
       </c>
-      <c r="C152" s="9" t="inlineStr">
+      <c r="C155" s="9" t="inlineStr">
         <is>
           <t>别忘了茶</t>
         </is>
       </c>
-      <c r="D152" s="9" t="inlineStr">
+      <c r="D155" s="9" t="inlineStr">
         <is>
           <t>8부 10·12화 변형</t>
         </is>
       </c>
-      <c r="E152" s="9" t="inlineStr">
+      <c r="E155" s="9" t="inlineStr">
         <is>
           <t>추모의 밤, 우슈전의 '别忘了茶'가 고통을 안고 온 사람에게 먼저 차를 내라는 뜻임이 해독된다. 폭발 자금의 지갑 구옌자오는 이미 해외로 떠났다.</t>
         </is>
       </c>
-      <c r="F152" s="9" t="inlineStr"/>
-    </row>
-    <row r="153">
-      <c r="A153" s="4" t="inlineStr">
-        <is>
-          <t>9부 1화</t>
-        </is>
-      </c>
-      <c r="B153" s="4" t="inlineStr">
-        <is>
-          <t>두 번째 임기</t>
-        </is>
-      </c>
-      <c r="C153" s="4" t="inlineStr">
-        <is>
-          <t>第二任期</t>
-        </is>
-      </c>
-      <c r="D153" s="4" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="E153" s="4" t="inlineStr">
-        <is>
-          <t>2기 첫날, 그는 정치국 회의록에 '5년 뒤 떠난다'는 문장을 남기고 공개한다. 박수는 드문드문하다.</t>
-        </is>
-      </c>
-      <c r="F153" s="4" t="inlineStr"/>
-    </row>
-    <row r="154">
-      <c r="A154" s="4" t="inlineStr">
-        <is>
-          <t>9부 2화</t>
-        </is>
-      </c>
-      <c r="B154" s="4" t="inlineStr">
-        <is>
-          <t>고향의 물</t>
-        </is>
-      </c>
-      <c r="C154" s="4" t="inlineStr">
-        <is>
-          <t>故乡的水</t>
-        </is>
-      </c>
-      <c r="D154" s="4" t="inlineStr">
-        <is>
-          <t>9부 2화 변형</t>
-        </is>
-      </c>
-      <c r="E154" s="4" t="inlineStr">
-        <is>
-          <t>기록적 폭우로 창촨 화학단지가 잠길 위기. 그가 고향으로 내려가 1부의 사람들을 다시 만난다.</t>
-        </is>
-      </c>
-      <c r="F154" s="4" t="inlineStr"/>
-    </row>
-    <row r="155">
-      <c r="A155" s="4" t="inlineStr">
-        <is>
-          <t>9부 3화</t>
-        </is>
-      </c>
-      <c r="B155" s="4" t="inlineStr">
-        <is>
-          <t>낙인</t>
-        </is>
-      </c>
-      <c r="C155" s="4" t="inlineStr">
-        <is>
-          <t>烙印</t>
-        </is>
-      </c>
-      <c r="D155" s="4" t="inlineStr">
-        <is>
-          <t>9부 3화 변형</t>
-        </is>
-      </c>
-      <c r="E155" s="4" t="inlineStr">
-        <is>
-          <t>'해외 세력' 낙인 조례가 폐지되고 명등 변호사들이 자격을 되찾는다. 리위퉁이 눈물을 보인다. 사면을 신청하지 않은 쑤민의 이름만 명단에 없다.</t>
-        </is>
-      </c>
-      <c r="F155" s="4" t="inlineStr"/>
+      <c r="F155" s="9" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="4" t="inlineStr">
         <is>
-          <t>9부 4화</t>
+          <t>9부 1화</t>
         </is>
       </c>
       <c r="B156" s="4" t="inlineStr">
         <is>
-          <t>퇴역군인의 재판</t>
+          <t>두 번째 임기</t>
         </is>
       </c>
       <c r="C156" s="4" t="inlineStr">
         <is>
-          <t>退伍军人的审判</t>
+          <t>第二任期</t>
         </is>
       </c>
       <c r="D156" s="4" t="inlineStr">
         <is>
-          <t>9부 4화 변형</t>
+          <t>신규</t>
         </is>
       </c>
       <c r="E156" s="4" t="inlineStr">
         <is>
-          <t>생계가 무너진 퇴역군인이 광장에서 사람들을 다치게 한 '사회 보복' 사건의 재판. 그는 방청석에서, 피고인 쪽 공민 대리인 쑤민의 뒷모습을 본다.</t>
+          <t>2기 첫날, 그는 정치국 회의록에 '5년 뒤 떠난다'는 문장을 남기고 공개한다. 박수는 드문드문하다.</t>
         </is>
       </c>
       <c r="F156" s="4" t="inlineStr"/>
@@ -13706,27 +13658,27 @@
     <row r="157">
       <c r="A157" s="4" t="inlineStr">
         <is>
-          <t>9부 5화</t>
+          <t>9부 2화</t>
         </is>
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>부치지 못한 편지</t>
+          <t>고향의 물</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>未寄出的信</t>
+          <t>故乡的水</t>
         </is>
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>신규</t>
+          <t>9부 2화 변형</t>
         </is>
       </c>
       <c r="E157" s="4" t="inlineStr">
         <is>
-          <t>서랍의 편지가 마흔 통이 된다. '사면 신청 한 장이면 된다'고 쓰다가, 그것이 커팅웨가 내밀던 거래와 같은 문장임을 깨닫고 또 부치지 못한다.</t>
+          <t>기록적 폭우로 창촨 화학단지가 잠길 위기. 그가 고향으로 내려가 1부의 사람들을 다시 만난다.</t>
         </is>
       </c>
       <c r="F157" s="4" t="inlineStr"/>
@@ -13734,27 +13686,27 @@
     <row r="158">
       <c r="A158" s="4" t="inlineStr">
         <is>
-          <t>9부 6화</t>
+          <t>9부 3화</t>
         </is>
       </c>
       <c r="B158" s="4" t="inlineStr">
         <is>
-          <t>그림자의 윤곽</t>
+          <t>낙인</t>
         </is>
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
-          <t>阴影的轮廓</t>
+          <t>烙印</t>
         </is>
       </c>
       <c r="D158" s="4" t="inlineStr">
         <is>
-          <t>9부 7화 변형</t>
+          <t>9부 3화 변형</t>
         </is>
       </c>
       <c r="E158" s="4" t="inlineStr">
         <is>
-          <t>커팅웨가 조용히 숨지고 장례식에는 그만 온다. 남긴 봉투에는 강경파 명단과 한 줄. '규칙은 사람을 가리지 않는다, 당신도.'</t>
+          <t>'해외 세력' 낙인 조례가 폐지되고 명등 변호사들이 자격을 되찾는다. 리위퉁이 눈물을 보인다. 사면을 신청하지 않은 쑤민의 이름만 명단에 없다.</t>
         </is>
       </c>
       <c r="F158" s="4" t="inlineStr"/>
@@ -13762,27 +13714,27 @@
     <row r="159">
       <c r="A159" s="4" t="inlineStr">
         <is>
-          <t>9부 7화</t>
+          <t>9부 4화</t>
         </is>
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>구옌자오의 송환</t>
+          <t>퇴역군인의 재판</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>顾延昭被遣返</t>
+          <t>退伍军人的审判</t>
         </is>
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>9부 12화 변형</t>
+          <t>9부 4화 변형</t>
         </is>
       </c>
       <c r="E159" s="4" t="inlineStr">
         <is>
-          <t>해외 도주 몇 해 만에 구옌자오가 송환되어 우슈전 폭발 자금원으로 기소된다. 그의 옛 돈줄이 사오톄쥔 주변으로 옮겨 가 있었다.</t>
+          <t>생계가 무너진 퇴역군인이 광장에서 사람들을 다치게 한 '사회 보복' 사건의 재판. 그는 방청석에서, 피고인 쪽 공민 대리인 쑤민의 뒷모습을 본다.</t>
         </is>
       </c>
       <c r="F159" s="4" t="inlineStr"/>
@@ -13790,27 +13742,27 @@
     <row r="160">
       <c r="A160" s="4" t="inlineStr">
         <is>
-          <t>9부 8화</t>
+          <t>9부 5화</t>
         </is>
       </c>
       <c r="B160" s="4" t="inlineStr">
         <is>
-          <t>청시, 후계 후보로</t>
+          <t>부치지 못한 편지</t>
         </is>
       </c>
       <c r="C160" s="4" t="inlineStr">
         <is>
-          <t>程曦成为接班候选</t>
+          <t>未寄出的信</t>
         </is>
       </c>
       <c r="D160" s="4" t="inlineStr">
         <is>
-          <t>9부 5화 변형</t>
+          <t>신규</t>
         </is>
       </c>
       <c r="E160" s="4" t="inlineStr">
         <is>
-          <t>비밀 지명 대신 정치국 공개 경쟁 추천이 처음 열린다. 청시가 이기고, 진 성위서기는 불복 편지를 쓴다.</t>
+          <t>서랍의 편지가 마흔 통이 된다. '사면 신청 한 장이면 된다'고 쓰다가, 그것이 커팅웨가 내밀던 거래와 같은 문장임을 깨닫고 또 부치지 못한다.</t>
         </is>
       </c>
       <c r="F160" s="4" t="inlineStr"/>
@@ -13818,27 +13770,27 @@
     <row r="161">
       <c r="A161" s="4" t="inlineStr">
         <is>
-          <t>9부 9화</t>
+          <t>9부 6화</t>
         </is>
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>녜추</t>
+          <t>그림자의 윤곽</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>聂秋</t>
+          <t>阴影的轮廓</t>
         </is>
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>9부 9화 변형</t>
+          <t>9부 7화 변형</t>
         </is>
       </c>
       <c r="E161" s="4" t="inlineStr">
         <is>
-          <t>청시가 차기 판공청 주임 후보로 녜추를 고른다. 녜추는 '잉훠의 쑤민에게서 장부 읽는 법을 배웠다'고 말한다.</t>
+          <t>커팅웨가 조용히 숨지고 장례식에는 그만 온다. 남긴 봉투에는 강경파 명단과 한 줄. '규칙은 사람을 가리지 않는다, 당신도.'</t>
         </is>
       </c>
       <c r="F161" s="4" t="inlineStr"/>
@@ -13846,27 +13798,27 @@
     <row r="162">
       <c r="A162" s="4" t="inlineStr">
         <is>
-          <t>9부 10화</t>
+          <t>9부 7화</t>
         </is>
       </c>
       <c r="B162" s="4" t="inlineStr">
         <is>
-          <t>끝나지 않은 일</t>
+          <t>구옌자오의 송환</t>
         </is>
       </c>
       <c r="C162" s="4" t="inlineStr">
         <is>
-          <t>未竟之事</t>
+          <t>顾延昭被遣返</t>
         </is>
       </c>
       <c r="D162" s="4" t="inlineStr">
         <is>
-          <t>신규</t>
+          <t>9부 12화 변형</t>
         </is>
       </c>
       <c r="E162" s="4" t="inlineStr">
         <is>
-          <t>지방은행들에 2차 부실 조짐이 보이고 금융 개혁 2단계는 절반에 머문다. 측근들이 '이 일은 당신만 끝낼 수 있다'고 말하기 시작한다.</t>
+          <t>해외 도주 몇 해 만에 구옌자오가 송환되어 우슈전 폭발 자금원으로 기소된다. 그의 옛 돈줄이 사오톄쥔 주변으로 옮겨 가 있었다.</t>
         </is>
       </c>
       <c r="F162" s="4" t="inlineStr"/>
@@ -13874,27 +13826,27 @@
     <row r="163">
       <c r="A163" s="4" t="inlineStr">
         <is>
-          <t>9부 11화</t>
+          <t>9부 8화</t>
         </is>
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>3기를 준비하자</t>
+          <t>청시, 후계 후보로</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>准备第三届</t>
+          <t>程曦成为接班候选</t>
         </is>
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>신규</t>
+          <t>9부 5화 변형</t>
         </is>
       </c>
       <c r="E163" s="4" t="inlineStr">
         <is>
-          <t>사오톄쥔이 웨이창펑을 버리고 그를 찾아온다. '3기를 준비하십시오. 규칙은 위기 앞에서 잠시 쉬면 됩니다.' 그는 답하지 않는다.</t>
+          <t>비밀 지명 대신 정치국 공개 경쟁 추천이 처음 열린다. 청시가 이기고, 진 성위서기는 불복 편지를 쓴다.</t>
         </is>
       </c>
       <c r="F163" s="4" t="inlineStr"/>
@@ -13902,129 +13854,129 @@
     <row r="164">
       <c r="A164" s="4" t="inlineStr">
         <is>
+          <t>9부 9화</t>
+        </is>
+      </c>
+      <c r="B164" s="4" t="inlineStr">
+        <is>
+          <t>녜추</t>
+        </is>
+      </c>
+      <c r="C164" s="4" t="inlineStr">
+        <is>
+          <t>聂秋</t>
+        </is>
+      </c>
+      <c r="D164" s="4" t="inlineStr">
+        <is>
+          <t>9부 9화 변형</t>
+        </is>
+      </c>
+      <c r="E164" s="4" t="inlineStr">
+        <is>
+          <t>청시가 차기 판공청 주임 후보로 녜추를 고른다. 녜추는 '잉훠의 쑤민에게서 장부 읽는 법을 배웠다'고 말한다.</t>
+        </is>
+      </c>
+      <c r="F164" s="4" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="4" t="inlineStr">
+        <is>
+          <t>9부 10화</t>
+        </is>
+      </c>
+      <c r="B165" s="4" t="inlineStr">
+        <is>
+          <t>끝나지 않은 일</t>
+        </is>
+      </c>
+      <c r="C165" s="4" t="inlineStr">
+        <is>
+          <t>未竟之事</t>
+        </is>
+      </c>
+      <c r="D165" s="4" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="E165" s="4" t="inlineStr">
+        <is>
+          <t>지방은행들에 2차 부실 조짐이 보이고 금융 개혁 2단계는 절반에 머문다. 측근들이 '이 일은 당신만 끝낼 수 있다'고 말하기 시작한다.</t>
+        </is>
+      </c>
+      <c r="F165" s="4" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="4" t="inlineStr">
+        <is>
+          <t>9부 11화</t>
+        </is>
+      </c>
+      <c r="B166" s="4" t="inlineStr">
+        <is>
+          <t>3기를 준비하자</t>
+        </is>
+      </c>
+      <c r="C166" s="4" t="inlineStr">
+        <is>
+          <t>准备第三届</t>
+        </is>
+      </c>
+      <c r="D166" s="4" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="E166" s="4" t="inlineStr">
+        <is>
+          <t>사오톄쥔이 웨이창펑을 버리고 그를 찾아온다. '3기를 준비하십시오. 규칙은 위기 앞에서 잠시 쉬면 됩니다.' 그는 답하지 않는다.</t>
+        </is>
+      </c>
+      <c r="F166" s="4" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="4" t="inlineStr">
+        <is>
           <t>9부 12화</t>
         </is>
       </c>
-      <c r="B164" s="4" t="inlineStr">
+      <c r="B167" s="4" t="inlineStr">
         <is>
           <t>마지막 해의 시작</t>
         </is>
       </c>
-      <c r="C164" s="4" t="inlineStr">
+      <c r="C167" s="4" t="inlineStr">
         <is>
           <t>最后一年的开始</t>
         </is>
       </c>
-      <c r="D164" s="4" t="inlineStr">
+      <c r="D167" s="4" t="inlineStr">
         <is>
           <t>9부 1화 변형</t>
         </is>
       </c>
-      <c r="E164" s="4" t="inlineStr">
+      <c r="E167" s="4" t="inlineStr">
         <is>
           <t>퇴임까지 1년. 그는 사오톄쥔의 3기 메모를 파쇄기 앞까지 들고 갔다가, 부치지 못한 편지들이 든 서랍에 넣는다.</t>
         </is>
       </c>
-      <c r="F164" s="4" t="inlineStr"/>
-    </row>
-    <row r="165">
-      <c r="A165" s="9" t="inlineStr">
-        <is>
-          <t>10부 1화</t>
-        </is>
-      </c>
-      <c r="B165" s="9" t="inlineStr">
-        <is>
-          <t>물이 차오른다</t>
-        </is>
-      </c>
-      <c r="C165" s="9" t="inlineStr">
-        <is>
-          <t>水涨起来</t>
-        </is>
-      </c>
-      <c r="D165" s="9" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="E165" s="9" t="inlineStr">
-        <is>
-          <t>[쑤민] 대홍수와 함께 지방은행 예금 인출이 동결된다. 잉훠의 골목 창구 앞에 예금주들의 줄이 끝없이 늘어서고, 쑤민은 밤새 소장 양식을 복사한다.</t>
-        </is>
-      </c>
-      <c r="F165" s="9" t="inlineStr"/>
-    </row>
-    <row r="166">
-      <c r="A166" s="9" t="inlineStr">
-        <is>
-          <t>10부 2화</t>
-        </is>
-      </c>
-      <c r="B166" s="9" t="inlineStr">
-        <is>
-          <t>지금 떠나면</t>
-        </is>
-      </c>
-      <c r="C166" s="9" t="inlineStr">
-        <is>
-          <t>现在离开的话</t>
-        </is>
-      </c>
-      <c r="D166" s="9" t="inlineStr">
-        <is>
-          <t>7부 2화 변형</t>
-        </is>
-      </c>
-      <c r="E166" s="9" t="inlineStr">
-        <is>
-          <t>국가안전위원회의 밤. 은행 연쇄 동결과 제방 붕괴 보고 사이에서 그는 처음으로 생각한다. '지금 떠나면 다 무너진다.'</t>
-        </is>
-      </c>
-      <c r="F166" s="9" t="inlineStr"/>
-    </row>
-    <row r="167">
-      <c r="A167" s="9" t="inlineStr">
-        <is>
-          <t>10부 3화</t>
-        </is>
-      </c>
-      <c r="B167" s="9" t="inlineStr">
-        <is>
-          <t>간화이구의 마지막 말</t>
-        </is>
-      </c>
-      <c r="C167" s="9" t="inlineStr">
-        <is>
-          <t>甘怀谷的遗言</t>
-        </is>
-      </c>
-      <c r="D167" s="9" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="E167" s="9" t="inlineStr">
-        <is>
-          <t>병상의 간화이구가 '들어오는 법은 내가 가르쳤다, 나가는 법은 네가 보여 달라'고 말하고 숨을 거둔다. 그는 대답을 미룬다.</t>
-        </is>
-      </c>
-      <c r="F167" s="9" t="inlineStr"/>
+      <c r="F167" s="4" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="9" t="inlineStr">
         <is>
-          <t>10부 4화</t>
+          <t>10부 1화</t>
         </is>
       </c>
       <c r="B168" s="9" t="inlineStr">
         <is>
-          <t>한 임기만 더</t>
+          <t>물이 차오른다</t>
         </is>
       </c>
       <c r="C168" s="9" t="inlineStr">
         <is>
-          <t>再干一届</t>
+          <t>水涨起来</t>
         </is>
       </c>
       <c r="D168" s="9" t="inlineStr">
@@ -14034,7 +13986,7 @@
       </c>
       <c r="E168" s="9" t="inlineStr">
         <is>
-          <t>사오톄쥔의 측근들이 성 당위원회들에서 '연임 요청' 결의를 시작한다. 그는 막지도 승인하지도 않는다. 침묵이 신호가 된다.</t>
+          <t>[쑤민] 대홍수와 함께 지방은행 예금 인출이 동결된다. 잉훠의 골목 창구 앞에 예금주들의 줄이 끝없이 늘어서고, 쑤민은 밤새 소장 양식을 복사한다.</t>
         </is>
       </c>
       <c r="F168" s="9" t="inlineStr"/>
@@ -14042,27 +13994,27 @@
     <row r="169">
       <c r="A169" s="9" t="inlineStr">
         <is>
-          <t>10부 5화</t>
+          <t>10부 2화</t>
         </is>
       </c>
       <c r="B169" s="9" t="inlineStr">
         <is>
-          <t>공개 서한</t>
+          <t>지금 떠나면</t>
         </is>
       </c>
       <c r="C169" s="9" t="inlineStr">
         <is>
-          <t>公开信</t>
+          <t>现在离开的话</t>
         </is>
       </c>
       <c r="D169" s="9" t="inlineStr">
         <is>
-          <t>신규</t>
+          <t>7부 2화 변형</t>
         </is>
       </c>
       <c r="E169" s="9" t="inlineStr">
         <is>
-          <t>[쑤민] '당신이 쓴 8부의 조항을 다시 읽으라.' 쑤민의 공개 서한이 메이뤄란 편에, 그리고 인터넷에 동시에 오른다. 그날 밤 그녀는 다시 연금된다. 누가 지시했는지 아무도 모른다.</t>
+          <t>국가안전위원회의 밤. 은행 연쇄 동결과 제방 붕괴 보고 사이에서 그는 처음으로 생각한다. '지금 떠나면 다 무너진다.'</t>
         </is>
       </c>
       <c r="F169" s="9" t="inlineStr"/>
@@ -14070,17 +14022,17 @@
     <row r="170">
       <c r="A170" s="9" t="inlineStr">
         <is>
-          <t>10부 6화</t>
+          <t>10부 3화</t>
         </is>
       </c>
       <c r="B170" s="9" t="inlineStr">
         <is>
-          <t>선장을 바꾸지 않는다</t>
+          <t>간화이구의 마지막 말</t>
         </is>
       </c>
       <c r="C170" s="9" t="inlineStr">
         <is>
-          <t>不换船长</t>
+          <t>甘怀谷的遗言</t>
         </is>
       </c>
       <c r="D170" s="9" t="inlineStr">
@@ -14090,7 +14042,7 @@
       </c>
       <c r="E170" s="9" t="inlineStr">
         <is>
-          <t>관영매체가 '큰 배는 풍랑 속에서 선장을 바꾸지 않는다'고 쓰고, 연설 초안에 처음으로 '영수'라는 호칭이 붙어 올라온다. 그는 펜을 들었다가 지우지 않는다.</t>
+          <t>병상의 간화이구가 '들어오는 법은 내가 가르쳤다, 나가는 법은 네가 보여 달라'고 말하고 숨을 거둔다. 그는 대답을 미룬다.</t>
         </is>
       </c>
       <c r="F170" s="9" t="inlineStr"/>
@@ -14098,17 +14050,17 @@
     <row r="171">
       <c r="A171" s="9" t="inlineStr">
         <is>
-          <t>10부 7화</t>
+          <t>10부 4화</t>
         </is>
       </c>
       <c r="B171" s="9" t="inlineStr">
         <is>
-          <t>청시의 방문</t>
+          <t>한 임기만 더</t>
         </is>
       </c>
       <c r="C171" s="9" t="inlineStr">
         <is>
-          <t>程曦来访</t>
+          <t>再干一届</t>
         </is>
       </c>
       <c r="D171" s="9" t="inlineStr">
@@ -14118,7 +14070,7 @@
       </c>
       <c r="E171" s="9" t="inlineStr">
         <is>
-          <t>[쑤민] 연금된 쑤민의 집에 청시가 홀로 찾아온다. '해임 조항을 쓰자고 한 건 그였어요.' 쑤민이 처음으로 먼저 차를 내고, 둘은 조항을 한 줄씩 읽는다.</t>
+          <t>사오톄쥔의 측근들이 성 당위원회들에서 '연임 요청' 결의를 시작한다. 그는 막지도 승인하지도 않는다. 침묵이 신호가 된다.</t>
         </is>
       </c>
       <c r="F171" s="9" t="inlineStr"/>
@@ -14126,17 +14078,17 @@
     <row r="172">
       <c r="A172" s="9" t="inlineStr">
         <is>
-          <t>10부 8화</t>
+          <t>10부 5화</t>
         </is>
       </c>
       <c r="B172" s="9" t="inlineStr">
         <is>
-          <t>남방의 요양지</t>
+          <t>공개 서한</t>
         </is>
       </c>
       <c r="C172" s="9" t="inlineStr">
         <is>
-          <t>南方的疗养地</t>
+          <t>公开信</t>
         </is>
       </c>
       <c r="D172" s="9" t="inlineStr">
@@ -14146,7 +14098,7 @@
       </c>
       <c r="E172" s="9" t="inlineStr">
         <is>
-          <t>홍수 현장 시찰 뒤 남쪽 요양지 란산에 머무는 그에게 '홍수 보고' 명목의 정치국 확대회의 통지가 온다. 사오톄쥔이 경호부대 동원을 제안하고, 그는 거절한다.</t>
+          <t>[쑤민] '당신이 쓴 8부의 조항을 다시 읽으라.' 쑤민의 공개 서한이 메이뤄란 편에, 그리고 인터넷에 동시에 오른다. 그날 밤 그녀는 다시 연금된다. 누가 지시했는지 아무도 모른다.</t>
         </is>
       </c>
       <c r="F172" s="9" t="inlineStr"/>
@@ -14154,27 +14106,27 @@
     <row r="173">
       <c r="A173" s="9" t="inlineStr">
         <is>
-          <t>10부 9화</t>
+          <t>10부 6화</t>
         </is>
       </c>
       <c r="B173" s="9" t="inlineStr">
         <is>
-          <t>확대회의</t>
+          <t>선장을 바꾸지 않는다</t>
         </is>
       </c>
       <c r="C173" s="9" t="inlineStr">
         <is>
-          <t>扩大会议</t>
+          <t>不换船长</t>
         </is>
       </c>
       <c r="D173" s="9" t="inlineStr">
         <is>
-          <t>9부 10화 변형</t>
+          <t>신규</t>
         </is>
       </c>
       <c r="E173" s="9" t="inlineStr">
         <is>
-          <t>정치국원 3분의 1 이상이 해임 동의안을 발의했다. 웨이창펑이 그가 쓴 조항을 읽고 청시가 사유를 읽는다. 그는 변론하지 않는다. '규칙대로 하시오.'</t>
+          <t>관영매체가 '큰 배는 풍랑 속에서 선장을 바꾸지 않는다'고 쓰고, 연설 초안에 처음으로 '영수'라는 호칭이 붙어 올라온다. 그는 펜을 들었다가 지우지 않는다.</t>
         </is>
       </c>
       <c r="F173" s="9" t="inlineStr"/>
@@ -14182,27 +14134,27 @@
     <row r="174">
       <c r="A174" s="9" t="inlineStr">
         <is>
-          <t>10부 10화</t>
+          <t>10부 7화</t>
         </is>
       </c>
       <c r="B174" s="9" t="inlineStr">
         <is>
-          <t>중앙위원회 표결</t>
+          <t>청시의 방문</t>
         </is>
       </c>
       <c r="C174" s="9" t="inlineStr">
         <is>
-          <t>中央委员会表决</t>
+          <t>程曦来访</t>
         </is>
       </c>
       <c r="D174" s="9" t="inlineStr">
         <is>
-          <t>9부 11화 변형</t>
+          <t>신규</t>
         </is>
       </c>
       <c r="E174" s="9" t="inlineStr">
         <is>
-          <t>이튿날 전체회의 과반 표결로 해임된다. '건강상 이유'로 발표하자는 배려를 그가 거절한다. '규정에 따른 해임이라고 쓰시오.' 그의 마지막 결정이다.</t>
+          <t>[쑤민] 연금된 쑤민의 집에 청시가 홀로 찾아온다. '해임 조항을 쓰자고 한 건 그였어요.' 쑤민이 처음으로 먼저 차를 내고, 둘은 조항을 한 줄씩 읽는다.</t>
         </is>
       </c>
       <c r="F174" s="9" t="inlineStr"/>
@@ -14210,17 +14162,17 @@
     <row r="175">
       <c r="A175" s="9" t="inlineStr">
         <is>
-          <t>10부 11화</t>
+          <t>10부 8화</t>
         </is>
       </c>
       <c r="B175" s="9" t="inlineStr">
         <is>
-          <t>첫 번째 결정</t>
+          <t>남방의 요양지</t>
         </is>
       </c>
       <c r="C175" s="9" t="inlineStr">
         <is>
-          <t>第一个决定</t>
+          <t>南方的疗养地</t>
         </is>
       </c>
       <c r="D175" s="9" t="inlineStr">
@@ -14230,7 +14182,7 @@
       </c>
       <c r="E175" s="9" t="inlineStr">
         <is>
-          <t>[쑤민] 청시 지도부의 첫 결정은 쑤민과 잉훠 동료들의 법적 복권이다. 연금이 풀린 날, 쑤민은 복권 통지서를 들고 탕쉐의 무덤에 차 한 잔을 붓는다.</t>
+          <t>홍수 현장 시찰 뒤 남쪽 요양지 란산에 머무는 그에게 '홍수 보고' 명목의 정치국 확대회의 통지가 온다. 사오톄쥔이 경호부대 동원을 제안하고, 그는 거절한다.</t>
         </is>
       </c>
       <c r="F175" s="9" t="inlineStr"/>
@@ -14238,27 +14190,27 @@
     <row r="176">
       <c r="A176" s="9" t="inlineStr">
         <is>
-          <t>10부 12화</t>
+          <t>10부 9화</t>
         </is>
       </c>
       <c r="B176" s="9" t="inlineStr">
         <is>
-          <t>평당원</t>
+          <t>확대회의</t>
         </is>
       </c>
       <c r="C176" s="9" t="inlineStr">
         <is>
-          <t>普通党员</t>
+          <t>扩大会议</t>
         </is>
       </c>
       <c r="D176" s="9" t="inlineStr">
         <is>
-          <t>9부 12화 변형</t>
+          <t>9부 10화 변형</t>
         </is>
       </c>
       <c r="E176" s="9" t="inlineStr">
         <is>
-          <t>창촨의 낡은 아파트, 어머니가 문을 연다. 그는 지부 당원회의 맨 뒷자리에 앉고, 부치지 못한 편지 묶음을 메이뤄란에게 맡긴다. 사오톄쥔은 규정대로 조사를 받는다.</t>
+          <t>정치국원 3분의 1 이상이 해임 동의안을 발의했다. 웨이창펑이 그가 쓴 조항을 읽고 청시가 사유를 읽는다. 그는 변론하지 않는다. '규칙대로 하시오.'</t>
         </is>
       </c>
       <c r="F176" s="9" t="inlineStr"/>
@@ -14266,54 +14218,141 @@
     <row r="177">
       <c r="A177" s="9" t="inlineStr">
         <is>
+          <t>10부 10화</t>
+        </is>
+      </c>
+      <c r="B177" s="9" t="inlineStr">
+        <is>
+          <t>중앙위원회 표결</t>
+        </is>
+      </c>
+      <c r="C177" s="9" t="inlineStr">
+        <is>
+          <t>中央委员会表决</t>
+        </is>
+      </c>
+      <c r="D177" s="9" t="inlineStr">
+        <is>
+          <t>9부 11화 변형</t>
+        </is>
+      </c>
+      <c r="E177" s="9" t="inlineStr">
+        <is>
+          <t>이튿날 전체회의 과반 표결로 해임된다. '건강상 이유'로 발표하자는 배려를 그가 거절한다. '규정에 따른 해임이라고 쓰시오.' 그의 마지막 결정이다.</t>
+        </is>
+      </c>
+      <c r="F177" s="9" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="9" t="inlineStr">
+        <is>
+          <t>10부 11화</t>
+        </is>
+      </c>
+      <c r="B178" s="9" t="inlineStr">
+        <is>
+          <t>첫 번째 결정</t>
+        </is>
+      </c>
+      <c r="C178" s="9" t="inlineStr">
+        <is>
+          <t>第一个决定</t>
+        </is>
+      </c>
+      <c r="D178" s="9" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="E178" s="9" t="inlineStr">
+        <is>
+          <t>[쑤민] 청시 지도부의 첫 결정은 쑤민과 잉훠 동료들의 법적 복권이다. 연금이 풀린 날, 쑤민은 복권 통지서를 들고 탕쉐의 무덤에 차 한 잔을 붓는다.</t>
+        </is>
+      </c>
+      <c r="F178" s="9" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="9" t="inlineStr">
+        <is>
+          <t>10부 12화</t>
+        </is>
+      </c>
+      <c r="B179" s="9" t="inlineStr">
+        <is>
+          <t>평당원</t>
+        </is>
+      </c>
+      <c r="C179" s="9" t="inlineStr">
+        <is>
+          <t>普通党员</t>
+        </is>
+      </c>
+      <c r="D179" s="9" t="inlineStr">
+        <is>
+          <t>9부 12화 변형</t>
+        </is>
+      </c>
+      <c r="E179" s="9" t="inlineStr">
+        <is>
+          <t>창촨의 낡은 아파트, 어머니가 문을 연다. 그는 지부 당원회의 맨 뒷자리에 앉고, 부치지 못한 편지 묶음을 메이뤄란에게 맡긴다. 사오톄쥔은 규정대로 조사를 받는다.</t>
+        </is>
+      </c>
+      <c r="F179" s="9" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="9" t="inlineStr">
+        <is>
           <t>10부 에필로그</t>
         </is>
       </c>
-      <c r="B177" s="9" t="inlineStr">
+      <c r="B180" s="9" t="inlineStr">
         <is>
           <t>차례</t>
         </is>
       </c>
-      <c r="C177" s="9" t="inlineStr">
+      <c r="C180" s="9" t="inlineStr">
         <is>
           <t>轮到你了</t>
         </is>
       </c>
-      <c r="D177" s="9" t="inlineStr">
+      <c r="D180" s="9" t="inlineStr">
         <is>
           <t>9부 에필로그 변형</t>
         </is>
       </c>
-      <c r="E177" s="9" t="inlineStr">
+      <c r="E180" s="9" t="inlineStr">
         <is>
           <t>5년 뒤, 청시는 한 번의 임기 뒤 녜추에게 넘긴다. 창촨 법률원조 창구, 이웃 노인의 연금 사건으로 번호표를 든 평당원 선즈위안. 창구의 쑤민이 먼저 차를 따른다.</t>
         </is>
       </c>
-      <c r="F177" s="9" t="inlineStr"/>
+      <c r="F180" s="9" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="21">
+  <mergeCells count="24">
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="B16:F16"/>
+    <mergeCell ref="B22:F22"/>
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A55:F55"/>
     <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B21:F21"/>
     <mergeCell ref="B12:F12"/>
-    <mergeCell ref="A42:F42"/>
     <mergeCell ref="B11:F11"/>
-    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="B23:F23"/>
     <mergeCell ref="B14:F14"/>
     <mergeCell ref="B8:F8"/>
     <mergeCell ref="B17:F17"/>
     <mergeCell ref="B13:F13"/>
     <mergeCell ref="B10:F10"/>
     <mergeCell ref="B19:F19"/>
+    <mergeCell ref="A58:F58"/>
     <mergeCell ref="B9:F9"/>
     <mergeCell ref="B6:F6"/>
     <mergeCell ref="B20:F20"/>
     <mergeCell ref="B15:F15"/>
+    <mergeCell ref="A45:F45"/>
     <mergeCell ref="B5:F5"/>
+    <mergeCell ref="A25:F25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
